--- a/rådata.xlsx
+++ b/rådata.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://svenskidrott-my.sharepoint.com/personal/william_lind_rfsisu_se/Documents/Dokument/GitHub/RF-SISU Uppland/SocialaMedier/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="69" documentId="11_AD4D1D646341095ACB7000BA6D52DEAE693EDF20" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1FFD6BF7-FD9B-4C06-A8FA-92673EDFED1F}"/>
+  <xr:revisionPtr revIDLastSave="84" documentId="11_AD4D1D646341095ACB7000BA6D52DEAE693EDF20" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0B38672-22DD-4841-9895-692B789CB466}"/>
   <bookViews>
-    <workbookView xWindow="-165" yWindow="-165" windowWidth="29130" windowHeight="15810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31095" yWindow="3885" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="rådata" sheetId="2" r:id="rId1"/>
+    <sheet name="audience_age" sheetId="3" r:id="rId2"/>
+    <sheet name="audience_city" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="Externadata_1" localSheetId="0" hidden="1">rådata!$A$1:$R$194</definedName>
@@ -45,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1283" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1398" uniqueCount="445">
   <si>
     <t>Post ID</t>
   </si>
@@ -1941,12 +1943,91 @@
   <si>
     <t>https://www.facebook.com/rfsisu.uppland/posts/pfbid0sXXTBww8K3sThGyCbpsm5YgqUbeQXNZ4CT6xJVtognU5hmXhPDSqY2hKBwkCLuH1l</t>
   </si>
+  <si>
+    <t>source</t>
+  </si>
+  <si>
+    <t>gender</t>
+  </si>
+  <si>
+    <t>age group</t>
+  </si>
+  <si>
+    <t>share</t>
+  </si>
+  <si>
+    <t>Facebook</t>
+  </si>
+  <si>
+    <t>Män</t>
+  </si>
+  <si>
+    <t>18-24</t>
+  </si>
+  <si>
+    <t>25-34</t>
+  </si>
+  <si>
+    <t>35-44</t>
+  </si>
+  <si>
+    <t>45-54</t>
+  </si>
+  <si>
+    <t>55-64</t>
+  </si>
+  <si>
+    <t>65+</t>
+  </si>
+  <si>
+    <t>Kvinnor</t>
+  </si>
+  <si>
+    <t>Instagram</t>
+  </si>
+  <si>
+    <t>city</t>
+  </si>
+  <si>
+    <t>Uppsala</t>
+  </si>
+  <si>
+    <t>Enköping</t>
+  </si>
+  <si>
+    <t>Stockholm</t>
+  </si>
+  <si>
+    <t>Norrtälje</t>
+  </si>
+  <si>
+    <t>Östhammar</t>
+  </si>
+  <si>
+    <t>Tierp</t>
+  </si>
+  <si>
+    <t>Knivsta</t>
+  </si>
+  <si>
+    <t>Märsta</t>
+  </si>
+  <si>
+    <t>Bålsta</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1955,15 +2036,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1971,19 +2058,232 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -2056,15 +2356,15 @@
   <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{C90B5D49-AB1F-4335-B42C-D2577B4D70A7}" uniqueName="1" name="Post ID" queryTableFieldId="1"/>
     <tableColumn id="2" xr3:uid="{9B31438A-DD11-4B38-BF0C-BD8767BDCF6A}" uniqueName="2" name="Account ID" queryTableFieldId="2"/>
-    <tableColumn id="3" xr3:uid="{51B2F4DB-63A1-466B-8552-4E471F3D09D6}" uniqueName="3" name="Account username" queryTableFieldId="3" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{8E49FBF6-8C34-49C5-B5E8-FFB592466400}" uniqueName="4" name="Account name" queryTableFieldId="4" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{7D4D46B8-67DB-47B1-ABD1-C48285F63029}" uniqueName="5" name="Description" queryTableFieldId="5" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{51B2F4DB-63A1-466B-8552-4E471F3D09D6}" uniqueName="3" name="Account username" queryTableFieldId="3" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{8E49FBF6-8C34-49C5-B5E8-FFB592466400}" uniqueName="4" name="Account name" queryTableFieldId="4" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{7D4D46B8-67DB-47B1-ABD1-C48285F63029}" uniqueName="5" name="Description" queryTableFieldId="5" dataDxfId="9"/>
     <tableColumn id="6" xr3:uid="{1F16BC45-ABB4-4BA8-87CF-68E25829776A}" uniqueName="6" name="Duration (sec)" queryTableFieldId="6"/>
-    <tableColumn id="7" xr3:uid="{074856E4-65F1-441D-8274-D7EC751C0486}" uniqueName="7" name="Publish time" queryTableFieldId="7" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{73F6C7E8-BD0C-482C-BE77-B546574187BD}" uniqueName="8" name="Permalink" queryTableFieldId="8" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{48022356-12DA-4FBD-8EF9-8FE5E5D3AE62}" uniqueName="9" name="Post type" queryTableFieldId="9" dataDxfId="2"/>
-    <tableColumn id="10" xr3:uid="{2EC884EB-4540-4CD4-A22E-935AB27830E8}" uniqueName="10" name="Data comment" queryTableFieldId="10" dataDxfId="1"/>
-    <tableColumn id="11" xr3:uid="{1B165494-2DDC-4FA7-A61A-5688782A4637}" uniqueName="11" name="Date" queryTableFieldId="11" dataDxfId="0"/>
+    <tableColumn id="7" xr3:uid="{074856E4-65F1-441D-8274-D7EC751C0486}" uniqueName="7" name="Publish time" queryTableFieldId="7" dataDxfId="8"/>
+    <tableColumn id="8" xr3:uid="{73F6C7E8-BD0C-482C-BE77-B546574187BD}" uniqueName="8" name="Permalink" queryTableFieldId="8" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{48022356-12DA-4FBD-8EF9-8FE5E5D3AE62}" uniqueName="9" name="Post type" queryTableFieldId="9" dataDxfId="6"/>
+    <tableColumn id="10" xr3:uid="{2EC884EB-4540-4CD4-A22E-935AB27830E8}" uniqueName="10" name="Data comment" queryTableFieldId="10" dataDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{1B165494-2DDC-4FA7-A61A-5688782A4637}" uniqueName="11" name="Date" queryTableFieldId="11" dataDxfId="4"/>
     <tableColumn id="12" xr3:uid="{2CC4D11C-E0BE-423C-8B0B-AABBFB0A9829}" uniqueName="12" name="Views" queryTableFieldId="12"/>
     <tableColumn id="13" xr3:uid="{CAF05024-EFB7-457C-AE42-DBB403440A99}" uniqueName="13" name="Likes" queryTableFieldId="13"/>
     <tableColumn id="14" xr3:uid="{6727B6C1-4A23-41E0-877C-04BB65A26D4D}" uniqueName="14" name="Shares" queryTableFieldId="14"/>
@@ -2074,6 +2374,31 @@
     <tableColumn id="18" xr3:uid="{E2824714-943F-4CC5-8509-7DEFCDE21716}" uniqueName="18" name="Follows" queryTableFieldId="18"/>
     <tableColumn id="19" xr3:uid="{9E730C2E-2076-4B43-9FFD-2392AEDBE58B}" uniqueName="19" name="Total clicks" queryTableFieldId="19"/>
     <tableColumn id="20" xr3:uid="{E30B5316-A1FE-48B7-A972-E1E4719C2688}" uniqueName="20" name="Other Clicks" queryTableFieldId="20"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{74B36380-C14A-4B51-B7B9-4578C4B5B16F}" name="Tabell4" displayName="Tabell4" ref="A1:D25" totalsRowShown="0">
+  <autoFilter ref="A1:D25" xr:uid="{74B36380-C14A-4B51-B7B9-4578C4B5B16F}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{C1BCE54E-59BE-47BC-A4C6-B65CFE5C2792}" name="source"/>
+    <tableColumn id="2" xr3:uid="{71F85263-7621-46AA-83D9-B6A636D4B542}" name="gender"/>
+    <tableColumn id="3" xr3:uid="{6AAE86B7-68EF-4BFF-B513-BEBC6524EFC0}" name="age group" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{03A2E103-45B0-4B6C-86EC-BC908B215DD3}" name="share" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{0A977CD6-399F-4F9E-8661-BEBD25C898B7}" name="Tabell5" displayName="Tabell5" ref="A1:C19" totalsRowShown="0">
+  <autoFilter ref="A1:C19" xr:uid="{0A977CD6-399F-4F9E-8661-BEBD25C898B7}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{35D8F3E2-9DBD-42CE-9408-885120530DBB}" name="source"/>
+    <tableColumn id="2" xr3:uid="{49F298AA-68B1-4CFB-9B0E-68E2A8CB7AEC}" name="city" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{05F676CD-41B6-4863-953A-981D7A949520}" name="share" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2433,31 +2758,31 @@
       <c r="B2">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
         <v>20</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="1">
         <v>46014.168749999997</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" s="1" t="s">
+      <c r="J2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" t="s">
         <v>24</v>
       </c>
       <c r="L2">
@@ -2489,31 +2814,31 @@
       <c r="B3">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
         <v>25</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="1">
         <v>46013.163194444445</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" s="1" t="s">
+      <c r="J3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" t="s">
         <v>24</v>
       </c>
       <c r="L3">
@@ -2545,31 +2870,31 @@
       <c r="B4">
         <v>1.7841400120519908E+16</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" t="s">
         <v>30</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="1">
         <v>46010.495138888888</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" t="s">
         <v>31</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" t="s">
         <v>27</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K4" s="1" t="s">
+      <c r="J4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K4" t="s">
         <v>24</v>
       </c>
       <c r="L4">
@@ -2595,31 +2920,31 @@
       <c r="B5">
         <v>1.7841403061265124E+16</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" t="s">
         <v>34</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="1">
         <v>46000.157638888886</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" t="s">
         <v>35</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" t="s">
         <v>22</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K5" s="1" t="s">
+      <c r="J5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K5" t="s">
         <v>24</v>
       </c>
       <c r="L5">
@@ -2645,31 +2970,31 @@
       <c r="B6">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" t="s">
         <v>36</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="1">
         <v>45996.101388888892</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" t="s">
         <v>37</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" t="s">
         <v>22</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K6" s="1" t="s">
+      <c r="J6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K6" t="s">
         <v>24</v>
       </c>
       <c r="L6">
@@ -2701,31 +3026,31 @@
       <c r="B7">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="1" t="s">
+      <c r="D7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" t="s">
         <v>38</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="1">
         <v>45994.969444444447</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" t="s">
         <v>39</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="I7" t="s">
         <v>22</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K7" s="1" t="s">
+      <c r="J7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K7" t="s">
         <v>24</v>
       </c>
       <c r="L7">
@@ -2757,31 +3082,31 @@
       <c r="B8">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="1" t="s">
+      <c r="D8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" t="s">
         <v>40</v>
       </c>
       <c r="F8">
         <v>24</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="1">
         <v>45991.993750000001</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8" t="s">
         <v>41</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" t="s">
         <v>42</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K8" s="1" t="s">
+      <c r="J8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K8" t="s">
         <v>24</v>
       </c>
       <c r="L8">
@@ -2813,31 +3138,31 @@
       <c r="B9">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="1" t="s">
+      <c r="D9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" t="s">
         <v>43</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="1">
         <v>45971.281944444447</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="H9" t="s">
         <v>44</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="I9" t="s">
         <v>27</v>
       </c>
-      <c r="J9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K9" s="1" t="s">
+      <c r="J9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K9" t="s">
         <v>24</v>
       </c>
       <c r="L9">
@@ -2869,31 +3194,31 @@
       <c r="B10">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="1" t="s">
+      <c r="D10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" t="s">
         <v>45</v>
       </c>
       <c r="F10">
         <v>0</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="1">
         <v>45959.046527777777</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="H10" t="s">
         <v>46</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="I10" t="s">
         <v>27</v>
       </c>
-      <c r="J10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K10" s="1" t="s">
+      <c r="J10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K10" t="s">
         <v>24</v>
       </c>
       <c r="L10">
@@ -2925,31 +3250,31 @@
       <c r="B11">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="1" t="s">
+      <c r="D11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" t="s">
         <v>47</v>
       </c>
       <c r="F11">
         <v>27</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="1">
         <v>45945.040972222225</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="H11" t="s">
         <v>48</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="I11" t="s">
         <v>42</v>
       </c>
-      <c r="J11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K11" s="1" t="s">
+      <c r="J11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K11" t="s">
         <v>24</v>
       </c>
       <c r="L11">
@@ -2981,31 +3306,31 @@
       <c r="B12">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="1" t="s">
+      <c r="D12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" t="s">
         <v>49</v>
       </c>
       <c r="F12">
         <v>0</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="1">
         <v>45943.207638888889</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="H12" t="s">
         <v>50</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="I12" t="s">
         <v>27</v>
       </c>
-      <c r="J12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K12" s="1" t="s">
+      <c r="J12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K12" t="s">
         <v>24</v>
       </c>
       <c r="L12">
@@ -3037,31 +3362,31 @@
       <c r="B13">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E13" s="1" t="s">
+      <c r="D13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" t="s">
         <v>51</v>
       </c>
       <c r="F13">
         <v>0</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="1">
         <v>45932.069444444445</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="H13" t="s">
         <v>52</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="I13" t="s">
         <v>27</v>
       </c>
-      <c r="J13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K13" s="1" t="s">
+      <c r="J13" t="s">
+        <v>23</v>
+      </c>
+      <c r="K13" t="s">
         <v>24</v>
       </c>
       <c r="L13">
@@ -3093,31 +3418,31 @@
       <c r="B14">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14" s="1" t="s">
+      <c r="D14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" t="s">
         <v>53</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="1">
         <v>45931.147916666669</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="H14" t="s">
         <v>54</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="I14" t="s">
         <v>27</v>
       </c>
-      <c r="J14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K14" s="1" t="s">
+      <c r="J14" t="s">
+        <v>23</v>
+      </c>
+      <c r="K14" t="s">
         <v>24</v>
       </c>
       <c r="L14">
@@ -3149,31 +3474,31 @@
       <c r="B15">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15" s="1" t="s">
+      <c r="D15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" t="s">
         <v>55</v>
       </c>
       <c r="F15">
         <v>0</v>
       </c>
-      <c r="G15" s="2">
+      <c r="G15" s="1">
         <v>45925.309027777781</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="H15" t="s">
         <v>56</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="I15" t="s">
         <v>27</v>
       </c>
-      <c r="J15" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K15" s="1" t="s">
+      <c r="J15" t="s">
+        <v>23</v>
+      </c>
+      <c r="K15" t="s">
         <v>24</v>
       </c>
       <c r="L15">
@@ -3205,31 +3530,31 @@
       <c r="B16">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E16" s="1" t="s">
+      <c r="D16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" t="s">
         <v>57</v>
       </c>
       <c r="F16">
         <v>0</v>
       </c>
-      <c r="G16" s="2">
+      <c r="G16" s="1">
         <v>45923.094444444447</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="H16" t="s">
         <v>58</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="I16" t="s">
         <v>27</v>
       </c>
-      <c r="J16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K16" s="1" t="s">
+      <c r="J16" t="s">
+        <v>23</v>
+      </c>
+      <c r="K16" t="s">
         <v>24</v>
       </c>
       <c r="L16">
@@ -3261,31 +3586,31 @@
       <c r="B17">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E17" s="1" t="s">
+      <c r="D17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" t="s">
         <v>59</v>
       </c>
       <c r="F17">
         <v>45</v>
       </c>
-      <c r="G17" s="2">
+      <c r="G17" s="1">
         <v>45922.185416666667</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="H17" t="s">
         <v>60</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="I17" t="s">
         <v>42</v>
       </c>
-      <c r="J17" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K17" s="1" t="s">
+      <c r="J17" t="s">
+        <v>23</v>
+      </c>
+      <c r="K17" t="s">
         <v>24</v>
       </c>
       <c r="L17">
@@ -3317,31 +3642,31 @@
       <c r="B18">
         <v>1.7841448346134484E+16</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" t="s">
         <v>61</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" t="s">
         <v>62</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" t="s">
         <v>63</v>
       </c>
       <c r="F18">
         <v>0</v>
       </c>
-      <c r="G18" s="2">
+      <c r="G18" s="1">
         <v>45918.145138888889</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="H18" t="s">
         <v>64</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="I18" t="s">
         <v>27</v>
       </c>
-      <c r="J18" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K18" s="1" t="s">
+      <c r="J18" t="s">
+        <v>23</v>
+      </c>
+      <c r="K18" t="s">
         <v>24</v>
       </c>
       <c r="L18">
@@ -3367,31 +3692,31 @@
       <c r="B19">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E19" s="1" t="s">
+      <c r="D19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" t="s">
         <v>65</v>
       </c>
       <c r="F19">
         <v>0</v>
       </c>
-      <c r="G19" s="2">
+      <c r="G19" s="1">
         <v>45917.250694444447</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="H19" t="s">
         <v>66</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="I19" t="s">
         <v>22</v>
       </c>
-      <c r="J19" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K19" s="1" t="s">
+      <c r="J19" t="s">
+        <v>23</v>
+      </c>
+      <c r="K19" t="s">
         <v>24</v>
       </c>
       <c r="L19">
@@ -3423,31 +3748,31 @@
       <c r="B20">
         <v>1.7841448346134484E+16</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" t="s">
         <v>61</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" t="s">
         <v>62</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E20" t="s">
         <v>67</v>
       </c>
       <c r="F20">
         <v>7</v>
       </c>
-      <c r="G20" s="2">
+      <c r="G20" s="1">
         <v>45917.070138888892</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="H20" t="s">
         <v>68</v>
       </c>
-      <c r="I20" s="1" t="s">
+      <c r="I20" t="s">
         <v>42</v>
       </c>
-      <c r="J20" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K20" s="1" t="s">
+      <c r="J20" t="s">
+        <v>23</v>
+      </c>
+      <c r="K20" t="s">
         <v>24</v>
       </c>
       <c r="L20">
@@ -3473,31 +3798,31 @@
       <c r="B21">
         <v>1.7841448346134484E+16</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" t="s">
         <v>61</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" t="s">
         <v>62</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" t="s">
         <v>69</v>
       </c>
       <c r="F21">
         <v>0</v>
       </c>
-      <c r="G21" s="2">
+      <c r="G21" s="1">
         <v>45916.115277777775</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="H21" t="s">
         <v>70</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="I21" t="s">
         <v>27</v>
       </c>
-      <c r="J21" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K21" s="1" t="s">
+      <c r="J21" t="s">
+        <v>23</v>
+      </c>
+      <c r="K21" t="s">
         <v>24</v>
       </c>
       <c r="L21">
@@ -3523,31 +3848,31 @@
       <c r="B22">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" t="s">
         <v>18</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E22" s="1" t="s">
+      <c r="D22" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" t="s">
         <v>71</v>
       </c>
       <c r="F22">
         <v>0</v>
       </c>
-      <c r="G22" s="2">
+      <c r="G22" s="1">
         <v>45915.18472222222</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="H22" t="s">
         <v>72</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="I22" t="s">
         <v>22</v>
       </c>
-      <c r="J22" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K22" s="1" t="s">
+      <c r="J22" t="s">
+        <v>23</v>
+      </c>
+      <c r="K22" t="s">
         <v>24</v>
       </c>
       <c r="L22">
@@ -3579,31 +3904,31 @@
       <c r="B23">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E23" s="1" t="s">
+      <c r="D23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" t="s">
         <v>73</v>
       </c>
       <c r="F23">
         <v>0</v>
       </c>
-      <c r="G23" s="2">
+      <c r="G23" s="1">
         <v>45911.052083333336</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="H23" t="s">
         <v>74</v>
       </c>
-      <c r="I23" s="1" t="s">
+      <c r="I23" t="s">
         <v>27</v>
       </c>
-      <c r="J23" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K23" s="1" t="s">
+      <c r="J23" t="s">
+        <v>23</v>
+      </c>
+      <c r="K23" t="s">
         <v>24</v>
       </c>
       <c r="L23">
@@ -3635,31 +3960,31 @@
       <c r="B24">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" t="s">
         <v>18</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E24" s="1" t="s">
+      <c r="D24" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" t="s">
         <v>75</v>
       </c>
       <c r="F24">
         <v>0</v>
       </c>
-      <c r="G24" s="2">
+      <c r="G24" s="1">
         <v>45910.052083333336</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="H24" t="s">
         <v>76</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="I24" t="s">
         <v>27</v>
       </c>
-      <c r="J24" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K24" s="1" t="s">
+      <c r="J24" t="s">
+        <v>23</v>
+      </c>
+      <c r="K24" t="s">
         <v>24</v>
       </c>
       <c r="L24">
@@ -3691,31 +4016,31 @@
       <c r="B25">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" t="s">
         <v>18</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E25" s="1" t="s">
+      <c r="D25" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" t="s">
         <v>77</v>
       </c>
       <c r="F25">
         <v>0</v>
       </c>
-      <c r="G25" s="2">
+      <c r="G25" s="1">
         <v>45908.238888888889</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="H25" t="s">
         <v>78</v>
       </c>
-      <c r="I25" s="1" t="s">
+      <c r="I25" t="s">
         <v>27</v>
       </c>
-      <c r="J25" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K25" s="1" t="s">
+      <c r="J25" t="s">
+        <v>23</v>
+      </c>
+      <c r="K25" t="s">
         <v>24</v>
       </c>
       <c r="L25">
@@ -3747,31 +4072,31 @@
       <c r="B26">
         <v>1.7841403849864212E+16</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" t="s">
         <v>79</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" t="s">
         <v>80</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E26" t="s">
         <v>81</v>
       </c>
       <c r="F26">
         <v>43</v>
       </c>
-      <c r="G26" s="2">
+      <c r="G26" s="1">
         <v>45908.057638888888</v>
       </c>
-      <c r="H26" s="1" t="s">
+      <c r="H26" t="s">
         <v>82</v>
       </c>
-      <c r="I26" s="1" t="s">
+      <c r="I26" t="s">
         <v>42</v>
       </c>
-      <c r="J26" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K26" s="1" t="s">
+      <c r="J26" t="s">
+        <v>23</v>
+      </c>
+      <c r="K26" t="s">
         <v>24</v>
       </c>
       <c r="L26">
@@ -3797,31 +4122,31 @@
       <c r="B27">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" t="s">
         <v>18</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E27" s="1" t="s">
+      <c r="D27" t="s">
+        <v>19</v>
+      </c>
+      <c r="E27" t="s">
         <v>83</v>
       </c>
       <c r="F27">
         <v>0</v>
       </c>
-      <c r="G27" s="2">
+      <c r="G27" s="1">
         <v>45905.150694444441</v>
       </c>
-      <c r="H27" s="1" t="s">
+      <c r="H27" t="s">
         <v>84</v>
       </c>
-      <c r="I27" s="1" t="s">
+      <c r="I27" t="s">
         <v>27</v>
       </c>
-      <c r="J27" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K27" s="1" t="s">
+      <c r="J27" t="s">
+        <v>23</v>
+      </c>
+      <c r="K27" t="s">
         <v>24</v>
       </c>
       <c r="L27">
@@ -3853,31 +4178,31 @@
       <c r="B28">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" t="s">
         <v>18</v>
       </c>
-      <c r="D28" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E28" s="1" t="s">
+      <c r="D28" t="s">
+        <v>19</v>
+      </c>
+      <c r="E28" t="s">
         <v>85</v>
       </c>
       <c r="F28">
         <v>0</v>
       </c>
-      <c r="G28" s="2">
+      <c r="G28" s="1">
         <v>45899.229166666664</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="H28" t="s">
         <v>86</v>
       </c>
-      <c r="I28" s="1" t="s">
+      <c r="I28" t="s">
         <v>27</v>
       </c>
-      <c r="J28" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K28" s="1" t="s">
+      <c r="J28" t="s">
+        <v>23</v>
+      </c>
+      <c r="K28" t="s">
         <v>24</v>
       </c>
       <c r="L28">
@@ -3909,31 +4234,31 @@
       <c r="B29">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" t="s">
         <v>18</v>
       </c>
-      <c r="D29" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E29" s="1" t="s">
+      <c r="D29" t="s">
+        <v>19</v>
+      </c>
+      <c r="E29" t="s">
         <v>87</v>
       </c>
       <c r="F29">
         <v>0</v>
       </c>
-      <c r="G29" s="2">
+      <c r="G29" s="1">
         <v>45898.099305555559</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="H29" t="s">
         <v>88</v>
       </c>
-      <c r="I29" s="1" t="s">
+      <c r="I29" t="s">
         <v>22</v>
       </c>
-      <c r="J29" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K29" s="1" t="s">
+      <c r="J29" t="s">
+        <v>23</v>
+      </c>
+      <c r="K29" t="s">
         <v>24</v>
       </c>
       <c r="L29">
@@ -3965,31 +4290,31 @@
       <c r="B30">
         <v>1.7841401157756682E+16</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" t="s">
         <v>89</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" t="s">
         <v>90</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="E30" t="s">
         <v>91</v>
       </c>
       <c r="F30">
         <v>32</v>
       </c>
-      <c r="G30" s="2">
+      <c r="G30" s="1">
         <v>45890.040972222225</v>
       </c>
-      <c r="H30" s="1" t="s">
+      <c r="H30" t="s">
         <v>92</v>
       </c>
-      <c r="I30" s="1" t="s">
+      <c r="I30" t="s">
         <v>42</v>
       </c>
-      <c r="J30" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K30" s="1" t="s">
+      <c r="J30" t="s">
+        <v>23</v>
+      </c>
+      <c r="K30" t="s">
         <v>24</v>
       </c>
       <c r="L30">
@@ -4015,31 +4340,31 @@
       <c r="B31">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" t="s">
         <v>18</v>
       </c>
-      <c r="D31" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E31" s="1" t="s">
+      <c r="D31" t="s">
+        <v>19</v>
+      </c>
+      <c r="E31" t="s">
         <v>93</v>
       </c>
       <c r="F31">
         <v>0</v>
       </c>
-      <c r="G31" s="2">
+      <c r="G31" s="1">
         <v>45826.246527777781</v>
       </c>
-      <c r="H31" s="1" t="s">
+      <c r="H31" t="s">
         <v>94</v>
       </c>
-      <c r="I31" s="1" t="s">
+      <c r="I31" t="s">
         <v>27</v>
       </c>
-      <c r="J31" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K31" s="1" t="s">
+      <c r="J31" t="s">
+        <v>23</v>
+      </c>
+      <c r="K31" t="s">
         <v>24</v>
       </c>
       <c r="L31">
@@ -4071,31 +4396,31 @@
       <c r="B32">
         <v>1.7841404375378016E+16</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" t="s">
         <v>95</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" t="s">
         <v>96</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="E32" t="s">
         <v>97</v>
       </c>
       <c r="F32">
         <v>32</v>
       </c>
-      <c r="G32" s="2">
+      <c r="G32" s="1">
         <v>45804.102083333331</v>
       </c>
-      <c r="H32" s="1" t="s">
+      <c r="H32" t="s">
         <v>98</v>
       </c>
-      <c r="I32" s="1" t="s">
+      <c r="I32" t="s">
         <v>42</v>
       </c>
-      <c r="J32" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K32" s="1" t="s">
+      <c r="J32" t="s">
+        <v>23</v>
+      </c>
+      <c r="K32" t="s">
         <v>24</v>
       </c>
       <c r="L32">
@@ -4121,31 +4446,31 @@
       <c r="B33">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" t="s">
         <v>18</v>
       </c>
-      <c r="D33" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E33" s="1" t="s">
+      <c r="D33" t="s">
+        <v>19</v>
+      </c>
+      <c r="E33" t="s">
         <v>99</v>
       </c>
       <c r="F33">
         <v>56</v>
       </c>
-      <c r="G33" s="2">
+      <c r="G33" s="1">
         <v>45803.986805555556</v>
       </c>
-      <c r="H33" s="1" t="s">
+      <c r="H33" t="s">
         <v>100</v>
       </c>
-      <c r="I33" s="1" t="s">
+      <c r="I33" t="s">
         <v>42</v>
       </c>
-      <c r="J33" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K33" s="1" t="s">
+      <c r="J33" t="s">
+        <v>23</v>
+      </c>
+      <c r="K33" t="s">
         <v>24</v>
       </c>
       <c r="L33">
@@ -4177,31 +4502,31 @@
       <c r="B34">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" t="s">
         <v>18</v>
       </c>
-      <c r="D34" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E34" s="1" t="s">
+      <c r="D34" t="s">
+        <v>19</v>
+      </c>
+      <c r="E34" t="s">
         <v>101</v>
       </c>
       <c r="F34">
         <v>0</v>
       </c>
-      <c r="G34" s="2">
+      <c r="G34" s="1">
         <v>45800.045138888891</v>
       </c>
-      <c r="H34" s="1" t="s">
+      <c r="H34" t="s">
         <v>102</v>
       </c>
-      <c r="I34" s="1" t="s">
+      <c r="I34" t="s">
         <v>27</v>
       </c>
-      <c r="J34" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K34" s="1" t="s">
+      <c r="J34" t="s">
+        <v>23</v>
+      </c>
+      <c r="K34" t="s">
         <v>24</v>
       </c>
       <c r="L34">
@@ -4233,31 +4558,31 @@
       <c r="B35">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" t="s">
         <v>18</v>
       </c>
-      <c r="D35" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E35" s="1" t="s">
+      <c r="D35" t="s">
+        <v>19</v>
+      </c>
+      <c r="E35" t="s">
         <v>103</v>
       </c>
       <c r="F35">
         <v>0</v>
       </c>
-      <c r="G35" s="2">
+      <c r="G35" s="1">
         <v>45783.994444444441</v>
       </c>
-      <c r="H35" s="1" t="s">
+      <c r="H35" t="s">
         <v>104</v>
       </c>
-      <c r="I35" s="1" t="s">
+      <c r="I35" t="s">
         <v>22</v>
       </c>
-      <c r="J35" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K35" s="1" t="s">
+      <c r="J35" t="s">
+        <v>23</v>
+      </c>
+      <c r="K35" t="s">
         <v>24</v>
       </c>
       <c r="L35">
@@ -4289,31 +4614,31 @@
       <c r="B36">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" t="s">
         <v>18</v>
       </c>
-      <c r="D36" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E36" s="1" t="s">
+      <c r="D36" t="s">
+        <v>19</v>
+      </c>
+      <c r="E36" t="s">
         <v>105</v>
       </c>
       <c r="F36">
         <v>0</v>
       </c>
-      <c r="G36" s="2">
+      <c r="G36" s="1">
         <v>45776.027777777781</v>
       </c>
-      <c r="H36" s="1" t="s">
+      <c r="H36" t="s">
         <v>106</v>
       </c>
-      <c r="I36" s="1" t="s">
+      <c r="I36" t="s">
         <v>27</v>
       </c>
-      <c r="J36" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K36" s="1" t="s">
+      <c r="J36" t="s">
+        <v>23</v>
+      </c>
+      <c r="K36" t="s">
         <v>24</v>
       </c>
       <c r="L36">
@@ -4345,31 +4670,31 @@
       <c r="B37">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" t="s">
         <v>18</v>
       </c>
-      <c r="D37" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E37" s="1" t="s">
+      <c r="D37" t="s">
+        <v>19</v>
+      </c>
+      <c r="E37" t="s">
         <v>107</v>
       </c>
       <c r="F37">
         <v>15</v>
       </c>
-      <c r="G37" s="2">
+      <c r="G37" s="1">
         <v>45770.990277777775</v>
       </c>
-      <c r="H37" s="1" t="s">
+      <c r="H37" t="s">
         <v>108</v>
       </c>
-      <c r="I37" s="1" t="s">
+      <c r="I37" t="s">
         <v>42</v>
       </c>
-      <c r="J37" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K37" s="1" t="s">
+      <c r="J37" t="s">
+        <v>23</v>
+      </c>
+      <c r="K37" t="s">
         <v>24</v>
       </c>
       <c r="L37">
@@ -4401,31 +4726,31 @@
       <c r="B38">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" t="s">
         <v>18</v>
       </c>
-      <c r="D38" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E38" s="1" t="s">
+      <c r="D38" t="s">
+        <v>19</v>
+      </c>
+      <c r="E38" t="s">
         <v>109</v>
       </c>
       <c r="F38">
         <v>73</v>
       </c>
-      <c r="G38" s="2">
+      <c r="G38" s="1">
         <v>45770.140972222223</v>
       </c>
-      <c r="H38" s="1" t="s">
+      <c r="H38" t="s">
         <v>110</v>
       </c>
-      <c r="I38" s="1" t="s">
+      <c r="I38" t="s">
         <v>42</v>
       </c>
-      <c r="J38" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K38" s="1" t="s">
+      <c r="J38" t="s">
+        <v>23</v>
+      </c>
+      <c r="K38" t="s">
         <v>24</v>
       </c>
       <c r="L38">
@@ -4457,31 +4782,31 @@
       <c r="B39">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" t="s">
         <v>18</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E39" s="1" t="s">
+      <c r="D39" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" t="s">
         <v>111</v>
       </c>
       <c r="F39">
         <v>0</v>
       </c>
-      <c r="G39" s="2">
+      <c r="G39" s="1">
         <v>45743.239583333336</v>
       </c>
-      <c r="H39" s="1" t="s">
+      <c r="H39" t="s">
         <v>112</v>
       </c>
-      <c r="I39" s="1" t="s">
+      <c r="I39" t="s">
         <v>27</v>
       </c>
-      <c r="J39" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K39" s="1" t="s">
+      <c r="J39" t="s">
+        <v>23</v>
+      </c>
+      <c r="K39" t="s">
         <v>24</v>
       </c>
       <c r="L39">
@@ -4513,31 +4838,31 @@
       <c r="B40">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" t="s">
         <v>18</v>
       </c>
-      <c r="D40" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E40" s="1" t="s">
+      <c r="D40" t="s">
+        <v>19</v>
+      </c>
+      <c r="E40" t="s">
         <v>113</v>
       </c>
       <c r="F40">
         <v>0</v>
       </c>
-      <c r="G40" s="2">
+      <c r="G40" s="1">
         <v>45737.074999999997</v>
       </c>
-      <c r="H40" s="1" t="s">
+      <c r="H40" t="s">
         <v>114</v>
       </c>
-      <c r="I40" s="1" t="s">
+      <c r="I40" t="s">
         <v>27</v>
       </c>
-      <c r="J40" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K40" s="1" t="s">
+      <c r="J40" t="s">
+        <v>23</v>
+      </c>
+      <c r="K40" t="s">
         <v>24</v>
       </c>
       <c r="L40">
@@ -4569,31 +4894,31 @@
       <c r="B41">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" t="s">
         <v>18</v>
       </c>
-      <c r="D41" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E41" s="1" t="s">
+      <c r="D41" t="s">
+        <v>19</v>
+      </c>
+      <c r="E41" t="s">
         <v>115</v>
       </c>
       <c r="F41">
         <v>39</v>
       </c>
-      <c r="G41" s="2">
+      <c r="G41" s="1">
         <v>45729.085416666669</v>
       </c>
-      <c r="H41" s="1" t="s">
+      <c r="H41" t="s">
         <v>116</v>
       </c>
-      <c r="I41" s="1" t="s">
+      <c r="I41" t="s">
         <v>42</v>
       </c>
-      <c r="J41" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K41" s="1" t="s">
+      <c r="J41" t="s">
+        <v>23</v>
+      </c>
+      <c r="K41" t="s">
         <v>24</v>
       </c>
       <c r="L41">
@@ -4625,31 +4950,31 @@
       <c r="B42">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" t="s">
         <v>18</v>
       </c>
-      <c r="D42" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E42" s="1" t="s">
+      <c r="D42" t="s">
+        <v>19</v>
+      </c>
+      <c r="E42" t="s">
         <v>117</v>
       </c>
       <c r="F42">
         <v>0</v>
       </c>
-      <c r="G42" s="2">
+      <c r="G42" s="1">
         <v>45721.987500000003</v>
       </c>
-      <c r="H42" s="1" t="s">
+      <c r="H42" t="s">
         <v>118</v>
       </c>
-      <c r="I42" s="1" t="s">
+      <c r="I42" t="s">
         <v>27</v>
       </c>
-      <c r="J42" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K42" s="1" t="s">
+      <c r="J42" t="s">
+        <v>23</v>
+      </c>
+      <c r="K42" t="s">
         <v>24</v>
       </c>
       <c r="L42">
@@ -4681,31 +5006,31 @@
       <c r="B43">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" t="s">
         <v>18</v>
       </c>
-      <c r="D43" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E43" s="1" t="s">
+      <c r="D43" t="s">
+        <v>19</v>
+      </c>
+      <c r="E43" t="s">
         <v>119</v>
       </c>
       <c r="F43">
         <v>0</v>
       </c>
-      <c r="G43" s="2">
+      <c r="G43" s="1">
         <v>45720.152777777781</v>
       </c>
-      <c r="H43" s="1" t="s">
+      <c r="H43" t="s">
         <v>120</v>
       </c>
-      <c r="I43" s="1" t="s">
+      <c r="I43" t="s">
         <v>27</v>
       </c>
-      <c r="J43" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K43" s="1" t="s">
+      <c r="J43" t="s">
+        <v>23</v>
+      </c>
+      <c r="K43" t="s">
         <v>24</v>
       </c>
       <c r="L43">
@@ -4737,31 +5062,31 @@
       <c r="B44">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" t="s">
         <v>18</v>
       </c>
-      <c r="D44" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E44" s="1" t="s">
+      <c r="D44" t="s">
+        <v>19</v>
+      </c>
+      <c r="E44" t="s">
         <v>121</v>
       </c>
       <c r="F44">
         <v>0</v>
       </c>
-      <c r="G44" s="2">
+      <c r="G44" s="1">
         <v>45698.011111111111</v>
       </c>
-      <c r="H44" s="1" t="s">
+      <c r="H44" t="s">
         <v>122</v>
       </c>
-      <c r="I44" s="1" t="s">
+      <c r="I44" t="s">
         <v>22</v>
       </c>
-      <c r="J44" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K44" s="1" t="s">
+      <c r="J44" t="s">
+        <v>23</v>
+      </c>
+      <c r="K44" t="s">
         <v>24</v>
       </c>
       <c r="L44">
@@ -4793,31 +5118,31 @@
       <c r="B45">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" t="s">
         <v>18</v>
       </c>
-      <c r="D45" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E45" s="1" t="s">
+      <c r="D45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E45" t="s">
         <v>123</v>
       </c>
       <c r="F45">
         <v>0</v>
       </c>
-      <c r="G45" s="2">
+      <c r="G45" s="1">
         <v>45693.261111111111</v>
       </c>
-      <c r="H45" s="1" t="s">
+      <c r="H45" t="s">
         <v>124</v>
       </c>
-      <c r="I45" s="1" t="s">
+      <c r="I45" t="s">
         <v>22</v>
       </c>
-      <c r="J45" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K45" s="1" t="s">
+      <c r="J45" t="s">
+        <v>23</v>
+      </c>
+      <c r="K45" t="s">
         <v>24</v>
       </c>
       <c r="L45">
@@ -4849,31 +5174,31 @@
       <c r="B46">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" t="s">
         <v>18</v>
       </c>
-      <c r="D46" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E46" s="1" t="s">
+      <c r="D46" t="s">
+        <v>19</v>
+      </c>
+      <c r="E46" t="s">
         <v>125</v>
       </c>
       <c r="F46">
         <v>39</v>
       </c>
-      <c r="G46" s="2">
+      <c r="G46" s="1">
         <v>45672.009027777778</v>
       </c>
-      <c r="H46" s="1" t="s">
+      <c r="H46" t="s">
         <v>126</v>
       </c>
-      <c r="I46" s="1" t="s">
+      <c r="I46" t="s">
         <v>42</v>
       </c>
-      <c r="J46" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K46" s="1" t="s">
+      <c r="J46" t="s">
+        <v>23</v>
+      </c>
+      <c r="K46" t="s">
         <v>24</v>
       </c>
       <c r="L46">
@@ -4905,31 +5230,31 @@
       <c r="B47">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" t="s">
         <v>18</v>
       </c>
-      <c r="D47" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E47" s="1" t="s">
+      <c r="D47" t="s">
+        <v>19</v>
+      </c>
+      <c r="E47" t="s">
         <v>127</v>
       </c>
       <c r="F47">
         <v>48</v>
       </c>
-      <c r="G47" s="2">
+      <c r="G47" s="1">
         <v>45313.979861111111</v>
       </c>
-      <c r="H47" s="1" t="s">
+      <c r="H47" t="s">
         <v>128</v>
       </c>
-      <c r="I47" s="1" t="s">
+      <c r="I47" t="s">
         <v>42</v>
       </c>
-      <c r="J47" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K47" s="1" t="s">
+      <c r="J47" t="s">
+        <v>23</v>
+      </c>
+      <c r="K47" t="s">
         <v>24</v>
       </c>
       <c r="M47">
@@ -4958,31 +5283,31 @@
       <c r="B48">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" t="s">
         <v>18</v>
       </c>
-      <c r="D48" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E48" s="1" t="s">
+      <c r="D48" t="s">
+        <v>19</v>
+      </c>
+      <c r="E48" t="s">
         <v>129</v>
       </c>
       <c r="F48">
         <v>0</v>
       </c>
-      <c r="G48" s="2">
+      <c r="G48" s="1">
         <v>45328.994444444441</v>
       </c>
-      <c r="H48" s="1" t="s">
+      <c r="H48" t="s">
         <v>130</v>
       </c>
-      <c r="I48" s="1" t="s">
+      <c r="I48" t="s">
         <v>22</v>
       </c>
-      <c r="J48" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K48" s="1" t="s">
+      <c r="J48" t="s">
+        <v>23</v>
+      </c>
+      <c r="K48" t="s">
         <v>24</v>
       </c>
       <c r="M48">
@@ -5011,31 +5336,31 @@
       <c r="B49">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" t="s">
         <v>18</v>
       </c>
-      <c r="D49" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E49" s="1" t="s">
+      <c r="D49" t="s">
+        <v>19</v>
+      </c>
+      <c r="E49" t="s">
         <v>131</v>
       </c>
       <c r="F49">
         <v>0</v>
       </c>
-      <c r="G49" s="2">
+      <c r="G49" s="1">
         <v>45337.990277777775</v>
       </c>
-      <c r="H49" s="1" t="s">
+      <c r="H49" t="s">
         <v>132</v>
       </c>
-      <c r="I49" s="1" t="s">
+      <c r="I49" t="s">
         <v>27</v>
       </c>
-      <c r="J49" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K49" s="1" t="s">
+      <c r="J49" t="s">
+        <v>23</v>
+      </c>
+      <c r="K49" t="s">
         <v>24</v>
       </c>
       <c r="M49">
@@ -5064,31 +5389,31 @@
       <c r="B50">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" t="s">
         <v>18</v>
       </c>
-      <c r="D50" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E50" s="1" t="s">
+      <c r="D50" t="s">
+        <v>19</v>
+      </c>
+      <c r="E50" t="s">
         <v>133</v>
       </c>
       <c r="F50">
         <v>0</v>
       </c>
-      <c r="G50" s="2">
+      <c r="G50" s="1">
         <v>45357.287499999999</v>
       </c>
-      <c r="H50" s="1" t="s">
+      <c r="H50" t="s">
         <v>134</v>
       </c>
-      <c r="I50" s="1" t="s">
+      <c r="I50" t="s">
         <v>22</v>
       </c>
-      <c r="J50" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K50" s="1" t="s">
+      <c r="J50" t="s">
+        <v>23</v>
+      </c>
+      <c r="K50" t="s">
         <v>24</v>
       </c>
       <c r="M50">
@@ -5117,31 +5442,31 @@
       <c r="B51">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C51" t="s">
         <v>18</v>
       </c>
-      <c r="D51" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E51" s="1" t="s">
+      <c r="D51" t="s">
+        <v>19</v>
+      </c>
+      <c r="E51" t="s">
         <v>135</v>
       </c>
       <c r="F51">
         <v>31</v>
       </c>
-      <c r="G51" s="2">
+      <c r="G51" s="1">
         <v>45364.255555555559</v>
       </c>
-      <c r="H51" s="1" t="s">
+      <c r="H51" t="s">
         <v>136</v>
       </c>
-      <c r="I51" s="1" t="s">
+      <c r="I51" t="s">
         <v>42</v>
       </c>
-      <c r="J51" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K51" s="1" t="s">
+      <c r="J51" t="s">
+        <v>23</v>
+      </c>
+      <c r="K51" t="s">
         <v>24</v>
       </c>
       <c r="M51">
@@ -5170,31 +5495,31 @@
       <c r="B52">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C52" t="s">
         <v>18</v>
       </c>
-      <c r="D52" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E52" s="1" t="s">
+      <c r="D52" t="s">
+        <v>19</v>
+      </c>
+      <c r="E52" t="s">
         <v>137</v>
       </c>
       <c r="F52">
         <v>0</v>
       </c>
-      <c r="G52" s="2">
+      <c r="G52" s="1">
         <v>45390.10833333333</v>
       </c>
-      <c r="H52" s="1" t="s">
+      <c r="H52" t="s">
         <v>138</v>
       </c>
-      <c r="I52" s="1" t="s">
+      <c r="I52" t="s">
         <v>27</v>
       </c>
-      <c r="J52" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K52" s="1" t="s">
+      <c r="J52" t="s">
+        <v>23</v>
+      </c>
+      <c r="K52" t="s">
         <v>24</v>
       </c>
       <c r="M52">
@@ -5223,31 +5548,31 @@
       <c r="B53">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C53" t="s">
         <v>18</v>
       </c>
-      <c r="D53" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E53" s="1" t="s">
+      <c r="D53" t="s">
+        <v>19</v>
+      </c>
+      <c r="E53" t="s">
         <v>139</v>
       </c>
       <c r="F53">
         <v>37</v>
       </c>
-      <c r="G53" s="2">
+      <c r="G53" s="1">
         <v>45394.21875</v>
       </c>
-      <c r="H53" s="1" t="s">
+      <c r="H53" t="s">
         <v>140</v>
       </c>
-      <c r="I53" s="1" t="s">
+      <c r="I53" t="s">
         <v>42</v>
       </c>
-      <c r="J53" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K53" s="1" t="s">
+      <c r="J53" t="s">
+        <v>23</v>
+      </c>
+      <c r="K53" t="s">
         <v>24</v>
       </c>
       <c r="M53">
@@ -5276,31 +5601,31 @@
       <c r="B54">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" t="s">
         <v>18</v>
       </c>
-      <c r="D54" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E54" s="1" t="s">
+      <c r="D54" t="s">
+        <v>19</v>
+      </c>
+      <c r="E54" t="s">
         <v>141</v>
       </c>
       <c r="F54">
         <v>48</v>
       </c>
-      <c r="G54" s="2">
+      <c r="G54" s="1">
         <v>45397.986111111109</v>
       </c>
-      <c r="H54" s="1" t="s">
+      <c r="H54" t="s">
         <v>142</v>
       </c>
-      <c r="I54" s="1" t="s">
+      <c r="I54" t="s">
         <v>42</v>
       </c>
-      <c r="J54" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K54" s="1" t="s">
+      <c r="J54" t="s">
+        <v>23</v>
+      </c>
+      <c r="K54" t="s">
         <v>24</v>
       </c>
       <c r="M54">
@@ -5329,31 +5654,31 @@
       <c r="B55">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" t="s">
         <v>18</v>
       </c>
-      <c r="D55" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E55" s="1" t="s">
+      <c r="D55" t="s">
+        <v>19</v>
+      </c>
+      <c r="E55" t="s">
         <v>143</v>
       </c>
       <c r="F55">
         <v>53</v>
       </c>
-      <c r="G55" s="2">
+      <c r="G55" s="1">
         <v>45399.091666666667</v>
       </c>
-      <c r="H55" s="1" t="s">
+      <c r="H55" t="s">
         <v>144</v>
       </c>
-      <c r="I55" s="1" t="s">
+      <c r="I55" t="s">
         <v>42</v>
       </c>
-      <c r="J55" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K55" s="1" t="s">
+      <c r="J55" t="s">
+        <v>23</v>
+      </c>
+      <c r="K55" t="s">
         <v>24</v>
       </c>
       <c r="M55">
@@ -5382,31 +5707,31 @@
       <c r="B56">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" t="s">
         <v>18</v>
       </c>
-      <c r="D56" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E56" s="1" t="s">
+      <c r="D56" t="s">
+        <v>19</v>
+      </c>
+      <c r="E56" t="s">
         <v>145</v>
       </c>
       <c r="F56">
         <v>0</v>
       </c>
-      <c r="G56" s="2">
+      <c r="G56" s="1">
         <v>45400.402777777781</v>
       </c>
-      <c r="H56" s="1" t="s">
+      <c r="H56" t="s">
         <v>146</v>
       </c>
-      <c r="I56" s="1" t="s">
+      <c r="I56" t="s">
         <v>22</v>
       </c>
-      <c r="J56" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K56" s="1" t="s">
+      <c r="J56" t="s">
+        <v>23</v>
+      </c>
+      <c r="K56" t="s">
         <v>24</v>
       </c>
       <c r="M56">
@@ -5435,31 +5760,31 @@
       <c r="B57">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" t="s">
         <v>18</v>
       </c>
-      <c r="D57" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E57" s="1" t="s">
+      <c r="D57" t="s">
+        <v>19</v>
+      </c>
+      <c r="E57" t="s">
         <v>147</v>
       </c>
       <c r="F57">
         <v>0</v>
       </c>
-      <c r="G57" s="2">
+      <c r="G57" s="1">
         <v>45401.131249999999</v>
       </c>
-      <c r="H57" s="1" t="s">
+      <c r="H57" t="s">
         <v>148</v>
       </c>
-      <c r="I57" s="1" t="s">
+      <c r="I57" t="s">
         <v>22</v>
       </c>
-      <c r="J57" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K57" s="1" t="s">
+      <c r="J57" t="s">
+        <v>23</v>
+      </c>
+      <c r="K57" t="s">
         <v>24</v>
       </c>
       <c r="M57">
@@ -5488,31 +5813,31 @@
       <c r="B58">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C58" t="s">
         <v>18</v>
       </c>
-      <c r="D58" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E58" s="1" t="s">
+      <c r="D58" t="s">
+        <v>19</v>
+      </c>
+      <c r="E58" t="s">
         <v>149</v>
       </c>
       <c r="F58">
         <v>0</v>
       </c>
-      <c r="G58" s="2">
+      <c r="G58" s="1">
         <v>45404.118055555555</v>
       </c>
-      <c r="H58" s="1" t="s">
+      <c r="H58" t="s">
         <v>150</v>
       </c>
-      <c r="I58" s="1" t="s">
+      <c r="I58" t="s">
         <v>22</v>
       </c>
-      <c r="J58" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K58" s="1" t="s">
+      <c r="J58" t="s">
+        <v>23</v>
+      </c>
+      <c r="K58" t="s">
         <v>24</v>
       </c>
       <c r="M58">
@@ -5541,31 +5866,31 @@
       <c r="B59">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C59" t="s">
         <v>18</v>
       </c>
-      <c r="D59" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E59" s="1" t="s">
+      <c r="D59" t="s">
+        <v>19</v>
+      </c>
+      <c r="E59" t="s">
         <v>151</v>
       </c>
       <c r="F59">
         <v>0</v>
       </c>
-      <c r="G59" s="2">
+      <c r="G59" s="1">
         <v>45415.112500000003</v>
       </c>
-      <c r="H59" s="1" t="s">
+      <c r="H59" t="s">
         <v>152</v>
       </c>
-      <c r="I59" s="1" t="s">
+      <c r="I59" t="s">
         <v>27</v>
       </c>
-      <c r="J59" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K59" s="1" t="s">
+      <c r="J59" t="s">
+        <v>23</v>
+      </c>
+      <c r="K59" t="s">
         <v>24</v>
       </c>
       <c r="M59">
@@ -5594,31 +5919,31 @@
       <c r="B60">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C60" t="s">
         <v>18</v>
       </c>
-      <c r="D60" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E60" s="1" t="s">
+      <c r="D60" t="s">
+        <v>19</v>
+      </c>
+      <c r="E60" t="s">
         <v>153</v>
       </c>
       <c r="F60">
         <v>0</v>
       </c>
-      <c r="G60" s="2">
+      <c r="G60" s="1">
         <v>45426.213194444441</v>
       </c>
-      <c r="H60" s="1" t="s">
+      <c r="H60" t="s">
         <v>154</v>
       </c>
-      <c r="I60" s="1" t="s">
+      <c r="I60" t="s">
         <v>27</v>
       </c>
-      <c r="J60" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K60" s="1" t="s">
+      <c r="J60" t="s">
+        <v>23</v>
+      </c>
+      <c r="K60" t="s">
         <v>24</v>
       </c>
       <c r="M60">
@@ -5647,31 +5972,31 @@
       <c r="B61">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C61" t="s">
         <v>18</v>
       </c>
-      <c r="D61" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E61" s="1" t="s">
+      <c r="D61" t="s">
+        <v>19</v>
+      </c>
+      <c r="E61" t="s">
         <v>155</v>
       </c>
       <c r="F61">
         <v>0</v>
       </c>
-      <c r="G61" s="2">
+      <c r="G61" s="1">
         <v>45432.241666666669</v>
       </c>
-      <c r="H61" s="1" t="s">
+      <c r="H61" t="s">
         <v>156</v>
       </c>
-      <c r="I61" s="1" t="s">
+      <c r="I61" t="s">
         <v>22</v>
       </c>
-      <c r="J61" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K61" s="1" t="s">
+      <c r="J61" t="s">
+        <v>23</v>
+      </c>
+      <c r="K61" t="s">
         <v>24</v>
       </c>
       <c r="M61">
@@ -5700,31 +6025,31 @@
       <c r="B62">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C62" t="s">
         <v>18</v>
       </c>
-      <c r="D62" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E62" s="1" t="s">
+      <c r="D62" t="s">
+        <v>19</v>
+      </c>
+      <c r="E62" t="s">
         <v>157</v>
       </c>
       <c r="F62">
         <v>0</v>
       </c>
-      <c r="G62" s="2">
+      <c r="G62" s="1">
         <v>45440.160416666666</v>
       </c>
-      <c r="H62" s="1" t="s">
+      <c r="H62" t="s">
         <v>158</v>
       </c>
-      <c r="I62" s="1" t="s">
+      <c r="I62" t="s">
         <v>22</v>
       </c>
-      <c r="J62" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K62" s="1" t="s">
+      <c r="J62" t="s">
+        <v>23</v>
+      </c>
+      <c r="K62" t="s">
         <v>24</v>
       </c>
       <c r="M62">
@@ -5753,31 +6078,31 @@
       <c r="B63">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C63" t="s">
         <v>18</v>
       </c>
-      <c r="D63" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E63" s="1" t="s">
+      <c r="D63" t="s">
+        <v>19</v>
+      </c>
+      <c r="E63" t="s">
         <v>159</v>
       </c>
       <c r="F63">
         <v>0</v>
       </c>
-      <c r="G63" s="2">
+      <c r="G63" s="1">
         <v>45460.339583333334</v>
       </c>
-      <c r="H63" s="1" t="s">
+      <c r="H63" t="s">
         <v>160</v>
       </c>
-      <c r="I63" s="1" t="s">
+      <c r="I63" t="s">
         <v>27</v>
       </c>
-      <c r="J63" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K63" s="1" t="s">
+      <c r="J63" t="s">
+        <v>23</v>
+      </c>
+      <c r="K63" t="s">
         <v>24</v>
       </c>
       <c r="M63">
@@ -5806,31 +6131,31 @@
       <c r="B64">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C64" t="s">
         <v>18</v>
       </c>
-      <c r="D64" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E64" s="1" t="s">
+      <c r="D64" t="s">
+        <v>19</v>
+      </c>
+      <c r="E64" t="s">
         <v>161</v>
       </c>
       <c r="F64">
         <v>29</v>
       </c>
-      <c r="G64" s="2">
+      <c r="G64" s="1">
         <v>45461.198611111111</v>
       </c>
-      <c r="H64" s="1" t="s">
+      <c r="H64" t="s">
         <v>162</v>
       </c>
-      <c r="I64" s="1" t="s">
+      <c r="I64" t="s">
         <v>42</v>
       </c>
-      <c r="J64" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K64" s="1" t="s">
+      <c r="J64" t="s">
+        <v>23</v>
+      </c>
+      <c r="K64" t="s">
         <v>24</v>
       </c>
       <c r="M64">
@@ -5859,31 +6184,31 @@
       <c r="B65">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C65" t="s">
         <v>18</v>
       </c>
-      <c r="D65" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E65" s="1" t="s">
+      <c r="D65" t="s">
+        <v>19</v>
+      </c>
+      <c r="E65" t="s">
         <v>163</v>
       </c>
       <c r="F65">
         <v>0</v>
       </c>
-      <c r="G65" s="2">
+      <c r="G65" s="1">
         <v>45474.254861111112</v>
       </c>
-      <c r="H65" s="1" t="s">
+      <c r="H65" t="s">
         <v>164</v>
       </c>
-      <c r="I65" s="1" t="s">
+      <c r="I65" t="s">
         <v>22</v>
       </c>
-      <c r="J65" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K65" s="1" t="s">
+      <c r="J65" t="s">
+        <v>23</v>
+      </c>
+      <c r="K65" t="s">
         <v>24</v>
       </c>
       <c r="M65">
@@ -5912,31 +6237,31 @@
       <c r="B66">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C66" t="s">
         <v>18</v>
       </c>
-      <c r="D66" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E66" s="1" t="s">
+      <c r="D66" t="s">
+        <v>19</v>
+      </c>
+      <c r="E66" t="s">
         <v>165</v>
       </c>
       <c r="F66">
         <v>0</v>
       </c>
-      <c r="G66" s="2">
+      <c r="G66" s="1">
         <v>45519.057638888888</v>
       </c>
-      <c r="H66" s="1" t="s">
+      <c r="H66" t="s">
         <v>166</v>
       </c>
-      <c r="I66" s="1" t="s">
+      <c r="I66" t="s">
         <v>22</v>
       </c>
-      <c r="J66" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K66" s="1" t="s">
+      <c r="J66" t="s">
+        <v>23</v>
+      </c>
+      <c r="K66" t="s">
         <v>24</v>
       </c>
       <c r="L66">
@@ -5968,31 +6293,31 @@
       <c r="B67">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C67" t="s">
         <v>18</v>
       </c>
-      <c r="D67" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E67" s="1" t="s">
+      <c r="D67" t="s">
+        <v>19</v>
+      </c>
+      <c r="E67" t="s">
         <v>167</v>
       </c>
       <c r="F67">
         <v>0</v>
       </c>
-      <c r="G67" s="2">
+      <c r="G67" s="1">
         <v>45520.104166666664</v>
       </c>
-      <c r="H67" s="1" t="s">
+      <c r="H67" t="s">
         <v>168</v>
       </c>
-      <c r="I67" s="1" t="s">
+      <c r="I67" t="s">
         <v>27</v>
       </c>
-      <c r="J67" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K67" s="1" t="s">
+      <c r="J67" t="s">
+        <v>23</v>
+      </c>
+      <c r="K67" t="s">
         <v>24</v>
       </c>
       <c r="L67">
@@ -6024,31 +6349,31 @@
       <c r="B68">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="C68" t="s">
         <v>18</v>
       </c>
-      <c r="D68" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E68" s="1" t="s">
+      <c r="D68" t="s">
+        <v>19</v>
+      </c>
+      <c r="E68" t="s">
         <v>169</v>
       </c>
       <c r="F68">
         <v>26</v>
       </c>
-      <c r="G68" s="2">
+      <c r="G68" s="1">
         <v>45524.196527777778</v>
       </c>
-      <c r="H68" s="1" t="s">
+      <c r="H68" t="s">
         <v>170</v>
       </c>
-      <c r="I68" s="1" t="s">
+      <c r="I68" t="s">
         <v>42</v>
       </c>
-      <c r="J68" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K68" s="1" t="s">
+      <c r="J68" t="s">
+        <v>23</v>
+      </c>
+      <c r="K68" t="s">
         <v>24</v>
       </c>
       <c r="L68">
@@ -6080,31 +6405,31 @@
       <c r="B69">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="C69" t="s">
         <v>18</v>
       </c>
-      <c r="D69" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E69" s="1" t="s">
+      <c r="D69" t="s">
+        <v>19</v>
+      </c>
+      <c r="E69" t="s">
         <v>171</v>
       </c>
       <c r="F69">
         <v>35</v>
       </c>
-      <c r="G69" s="2">
+      <c r="G69" s="1">
         <v>45533.00277777778</v>
       </c>
-      <c r="H69" s="1" t="s">
+      <c r="H69" t="s">
         <v>172</v>
       </c>
-      <c r="I69" s="1" t="s">
+      <c r="I69" t="s">
         <v>42</v>
       </c>
-      <c r="J69" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K69" s="1" t="s">
+      <c r="J69" t="s">
+        <v>23</v>
+      </c>
+      <c r="K69" t="s">
         <v>24</v>
       </c>
       <c r="L69">
@@ -6136,31 +6461,31 @@
       <c r="B70">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="C70" t="s">
         <v>18</v>
       </c>
-      <c r="D70" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E70" s="1" t="s">
+      <c r="D70" t="s">
+        <v>19</v>
+      </c>
+      <c r="E70" t="s">
         <v>173</v>
       </c>
       <c r="F70">
         <v>0</v>
       </c>
-      <c r="G70" s="2">
+      <c r="G70" s="1">
         <v>45535.247916666667</v>
       </c>
-      <c r="H70" s="1" t="s">
+      <c r="H70" t="s">
         <v>174</v>
       </c>
-      <c r="I70" s="1" t="s">
+      <c r="I70" t="s">
         <v>27</v>
       </c>
-      <c r="J70" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K70" s="1" t="s">
+      <c r="J70" t="s">
+        <v>23</v>
+      </c>
+      <c r="K70" t="s">
         <v>24</v>
       </c>
       <c r="L70">
@@ -6192,31 +6517,31 @@
       <c r="B71">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="C71" t="s">
         <v>18</v>
       </c>
-      <c r="D71" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E71" s="1" t="s">
+      <c r="D71" t="s">
+        <v>19</v>
+      </c>
+      <c r="E71" t="s">
         <v>175</v>
       </c>
       <c r="F71">
         <v>0</v>
       </c>
-      <c r="G71" s="2">
+      <c r="G71" s="1">
         <v>45538.249305555553</v>
       </c>
-      <c r="H71" s="1" t="s">
+      <c r="H71" t="s">
         <v>176</v>
       </c>
-      <c r="I71" s="1" t="s">
+      <c r="I71" t="s">
         <v>22</v>
       </c>
-      <c r="J71" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K71" s="1" t="s">
+      <c r="J71" t="s">
+        <v>23</v>
+      </c>
+      <c r="K71" t="s">
         <v>24</v>
       </c>
       <c r="L71">
@@ -6248,31 +6573,31 @@
       <c r="B72">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="C72" t="s">
         <v>18</v>
       </c>
-      <c r="D72" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E72" s="1" t="s">
+      <c r="D72" t="s">
+        <v>19</v>
+      </c>
+      <c r="E72" t="s">
         <v>177</v>
       </c>
       <c r="F72">
         <v>0</v>
       </c>
-      <c r="G72" s="2">
+      <c r="G72" s="1">
         <v>45544.054166666669</v>
       </c>
-      <c r="H72" s="1" t="s">
+      <c r="H72" t="s">
         <v>178</v>
       </c>
-      <c r="I72" s="1" t="s">
+      <c r="I72" t="s">
         <v>27</v>
       </c>
-      <c r="J72" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K72" s="1" t="s">
+      <c r="J72" t="s">
+        <v>23</v>
+      </c>
+      <c r="K72" t="s">
         <v>24</v>
       </c>
       <c r="L72">
@@ -6304,31 +6629,31 @@
       <c r="B73">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="C73" t="s">
         <v>18</v>
       </c>
-      <c r="D73" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E73" s="1" t="s">
+      <c r="D73" t="s">
+        <v>19</v>
+      </c>
+      <c r="E73" t="s">
         <v>179</v>
       </c>
       <c r="F73">
         <v>0</v>
       </c>
-      <c r="G73" s="2">
+      <c r="G73" s="1">
         <v>45545.28125</v>
       </c>
-      <c r="H73" s="1" t="s">
+      <c r="H73" t="s">
         <v>180</v>
       </c>
-      <c r="I73" s="1" t="s">
+      <c r="I73" t="s">
         <v>27</v>
       </c>
-      <c r="J73" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K73" s="1" t="s">
+      <c r="J73" t="s">
+        <v>23</v>
+      </c>
+      <c r="K73" t="s">
         <v>24</v>
       </c>
       <c r="L73">
@@ -6360,31 +6685,31 @@
       <c r="B74">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="C74" t="s">
         <v>18</v>
       </c>
-      <c r="D74" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E74" s="1" t="s">
+      <c r="D74" t="s">
+        <v>19</v>
+      </c>
+      <c r="E74" t="s">
         <v>181</v>
       </c>
       <c r="F74">
         <v>0</v>
       </c>
-      <c r="G74" s="2">
+      <c r="G74" s="1">
         <v>45551.129861111112</v>
       </c>
-      <c r="H74" s="1" t="s">
+      <c r="H74" t="s">
         <v>182</v>
       </c>
-      <c r="I74" s="1" t="s">
+      <c r="I74" t="s">
         <v>22</v>
       </c>
-      <c r="J74" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K74" s="1" t="s">
+      <c r="J74" t="s">
+        <v>23</v>
+      </c>
+      <c r="K74" t="s">
         <v>24</v>
       </c>
       <c r="L74">
@@ -6416,31 +6741,31 @@
       <c r="B75">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C75" t="s">
         <v>18</v>
       </c>
-      <c r="D75" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E75" s="1" t="s">
+      <c r="D75" t="s">
+        <v>19</v>
+      </c>
+      <c r="E75" t="s">
         <v>183</v>
       </c>
       <c r="F75">
         <v>0</v>
       </c>
-      <c r="G75" s="2">
+      <c r="G75" s="1">
         <v>45552.068749999999</v>
       </c>
-      <c r="H75" s="1" t="s">
+      <c r="H75" t="s">
         <v>184</v>
       </c>
-      <c r="I75" s="1" t="s">
+      <c r="I75" t="s">
         <v>22</v>
       </c>
-      <c r="J75" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K75" s="1" t="s">
+      <c r="J75" t="s">
+        <v>23</v>
+      </c>
+      <c r="K75" t="s">
         <v>24</v>
       </c>
       <c r="L75">
@@ -6472,31 +6797,31 @@
       <c r="B76">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="C76" t="s">
         <v>18</v>
       </c>
-      <c r="D76" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E76" s="1" t="s">
+      <c r="D76" t="s">
+        <v>19</v>
+      </c>
+      <c r="E76" t="s">
         <v>185</v>
       </c>
       <c r="F76">
         <v>0</v>
       </c>
-      <c r="G76" s="2">
+      <c r="G76" s="1">
         <v>45553.128472222219</v>
       </c>
-      <c r="H76" s="1" t="s">
+      <c r="H76" t="s">
         <v>186</v>
       </c>
-      <c r="I76" s="1" t="s">
+      <c r="I76" t="s">
         <v>22</v>
       </c>
-      <c r="J76" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K76" s="1" t="s">
+      <c r="J76" t="s">
+        <v>23</v>
+      </c>
+      <c r="K76" t="s">
         <v>24</v>
       </c>
       <c r="L76">
@@ -6528,31 +6853,31 @@
       <c r="B77">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="C77" t="s">
         <v>18</v>
       </c>
-      <c r="D77" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E77" s="1" t="s">
+      <c r="D77" t="s">
+        <v>19</v>
+      </c>
+      <c r="E77" t="s">
         <v>187</v>
       </c>
       <c r="F77">
         <v>0</v>
       </c>
-      <c r="G77" s="2">
+      <c r="G77" s="1">
         <v>45554.044444444444</v>
       </c>
-      <c r="H77" s="1" t="s">
+      <c r="H77" t="s">
         <v>188</v>
       </c>
-      <c r="I77" s="1" t="s">
+      <c r="I77" t="s">
         <v>27</v>
       </c>
-      <c r="J77" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K77" s="1" t="s">
+      <c r="J77" t="s">
+        <v>23</v>
+      </c>
+      <c r="K77" t="s">
         <v>24</v>
       </c>
       <c r="L77">
@@ -6584,31 +6909,31 @@
       <c r="B78">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="C78" t="s">
         <v>18</v>
       </c>
-      <c r="D78" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E78" s="1" t="s">
+      <c r="D78" t="s">
+        <v>19</v>
+      </c>
+      <c r="E78" t="s">
         <v>189</v>
       </c>
       <c r="F78">
         <v>0</v>
       </c>
-      <c r="G78" s="2">
+      <c r="G78" s="1">
         <v>45555.001388888886</v>
       </c>
-      <c r="H78" s="1" t="s">
+      <c r="H78" t="s">
         <v>190</v>
       </c>
-      <c r="I78" s="1" t="s">
+      <c r="I78" t="s">
         <v>27</v>
       </c>
-      <c r="J78" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K78" s="1" t="s">
+      <c r="J78" t="s">
+        <v>23</v>
+      </c>
+      <c r="K78" t="s">
         <v>24</v>
       </c>
       <c r="L78">
@@ -6640,31 +6965,31 @@
       <c r="B79">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="C79" t="s">
         <v>18</v>
       </c>
-      <c r="D79" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E79" s="1" t="s">
+      <c r="D79" t="s">
+        <v>19</v>
+      </c>
+      <c r="E79" t="s">
         <v>191</v>
       </c>
       <c r="F79">
         <v>15</v>
       </c>
-      <c r="G79" s="2">
+      <c r="G79" s="1">
         <v>45559.015277777777</v>
       </c>
-      <c r="H79" s="1" t="s">
+      <c r="H79" t="s">
         <v>192</v>
       </c>
-      <c r="I79" s="1" t="s">
+      <c r="I79" t="s">
         <v>42</v>
       </c>
-      <c r="J79" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K79" s="1" t="s">
+      <c r="J79" t="s">
+        <v>23</v>
+      </c>
+      <c r="K79" t="s">
         <v>24</v>
       </c>
       <c r="L79">
@@ -6696,31 +7021,31 @@
       <c r="B80">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C80" t="s">
         <v>18</v>
       </c>
-      <c r="D80" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E80" s="1" t="s">
+      <c r="D80" t="s">
+        <v>19</v>
+      </c>
+      <c r="E80" t="s">
         <v>193</v>
       </c>
       <c r="F80">
         <v>0</v>
       </c>
-      <c r="G80" s="2">
+      <c r="G80" s="1">
         <v>45562.007638888892</v>
       </c>
-      <c r="H80" s="1" t="s">
+      <c r="H80" t="s">
         <v>194</v>
       </c>
-      <c r="I80" s="1" t="s">
+      <c r="I80" t="s">
         <v>27</v>
       </c>
-      <c r="J80" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K80" s="1" t="s">
+      <c r="J80" t="s">
+        <v>23</v>
+      </c>
+      <c r="K80" t="s">
         <v>24</v>
       </c>
       <c r="L80">
@@ -6752,31 +7077,31 @@
       <c r="B81">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="C81" t="s">
         <v>18</v>
       </c>
-      <c r="D81" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E81" s="1" t="s">
+      <c r="D81" t="s">
+        <v>19</v>
+      </c>
+      <c r="E81" t="s">
         <v>195</v>
       </c>
       <c r="F81">
         <v>0</v>
       </c>
-      <c r="G81" s="2">
+      <c r="G81" s="1">
         <v>45563.074999999997</v>
       </c>
-      <c r="H81" s="1" t="s">
+      <c r="H81" t="s">
         <v>196</v>
       </c>
-      <c r="I81" s="1" t="s">
+      <c r="I81" t="s">
         <v>22</v>
       </c>
-      <c r="J81" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K81" s="1" t="s">
+      <c r="J81" t="s">
+        <v>23</v>
+      </c>
+      <c r="K81" t="s">
         <v>24</v>
       </c>
       <c r="L81">
@@ -6808,31 +7133,31 @@
       <c r="B82">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="C82" t="s">
         <v>18</v>
       </c>
-      <c r="D82" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E82" s="1" t="s">
+      <c r="D82" t="s">
+        <v>19</v>
+      </c>
+      <c r="E82" t="s">
         <v>197</v>
       </c>
       <c r="F82">
         <v>0</v>
       </c>
-      <c r="G82" s="2">
+      <c r="G82" s="1">
         <v>45568.99722222222</v>
       </c>
-      <c r="H82" s="1" t="s">
+      <c r="H82" t="s">
         <v>198</v>
       </c>
-      <c r="I82" s="1" t="s">
+      <c r="I82" t="s">
         <v>22</v>
       </c>
-      <c r="J82" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K82" s="1" t="s">
+      <c r="J82" t="s">
+        <v>23</v>
+      </c>
+      <c r="K82" t="s">
         <v>24</v>
       </c>
       <c r="L82">
@@ -6864,31 +7189,31 @@
       <c r="B83">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="C83" t="s">
         <v>18</v>
       </c>
-      <c r="D83" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E83" s="1" t="s">
+      <c r="D83" t="s">
+        <v>19</v>
+      </c>
+      <c r="E83" t="s">
         <v>199</v>
       </c>
       <c r="F83">
         <v>29</v>
       </c>
-      <c r="G83" s="2">
+      <c r="G83" s="1">
         <v>45569.17291666667</v>
       </c>
-      <c r="H83" s="1" t="s">
+      <c r="H83" t="s">
         <v>200</v>
       </c>
-      <c r="I83" s="1" t="s">
+      <c r="I83" t="s">
         <v>42</v>
       </c>
-      <c r="J83" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K83" s="1" t="s">
+      <c r="J83" t="s">
+        <v>23</v>
+      </c>
+      <c r="K83" t="s">
         <v>24</v>
       </c>
       <c r="L83">
@@ -6920,31 +7245,31 @@
       <c r="B84">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="C84" t="s">
         <v>18</v>
       </c>
-      <c r="D84" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E84" s="1" t="s">
+      <c r="D84" t="s">
+        <v>19</v>
+      </c>
+      <c r="E84" t="s">
         <v>201</v>
       </c>
       <c r="F84">
         <v>0</v>
       </c>
-      <c r="G84" s="2">
+      <c r="G84" s="1">
         <v>45578.996527777781</v>
       </c>
-      <c r="H84" s="1" t="s">
+      <c r="H84" t="s">
         <v>202</v>
       </c>
-      <c r="I84" s="1" t="s">
+      <c r="I84" t="s">
         <v>22</v>
       </c>
-      <c r="J84" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K84" s="1" t="s">
+      <c r="J84" t="s">
+        <v>23</v>
+      </c>
+      <c r="K84" t="s">
         <v>24</v>
       </c>
       <c r="L84">
@@ -6976,31 +7301,31 @@
       <c r="B85">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="C85" t="s">
         <v>18</v>
       </c>
-      <c r="D85" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E85" s="1" t="s">
+      <c r="D85" t="s">
+        <v>19</v>
+      </c>
+      <c r="E85" t="s">
         <v>203</v>
       </c>
       <c r="F85">
         <v>0</v>
       </c>
-      <c r="G85" s="2">
+      <c r="G85" s="1">
         <v>45580.270138888889</v>
       </c>
-      <c r="H85" s="1" t="s">
+      <c r="H85" t="s">
         <v>204</v>
       </c>
-      <c r="I85" s="1" t="s">
+      <c r="I85" t="s">
         <v>27</v>
       </c>
-      <c r="J85" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K85" s="1" t="s">
+      <c r="J85" t="s">
+        <v>23</v>
+      </c>
+      <c r="K85" t="s">
         <v>24</v>
       </c>
       <c r="L85">
@@ -7032,31 +7357,31 @@
       <c r="B86">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="C86" t="s">
         <v>18</v>
       </c>
-      <c r="D86" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E86" s="1" t="s">
+      <c r="D86" t="s">
+        <v>19</v>
+      </c>
+      <c r="E86" t="s">
         <v>205</v>
       </c>
       <c r="F86">
         <v>0</v>
       </c>
-      <c r="G86" s="2">
+      <c r="G86" s="1">
         <v>45581.006249999999</v>
       </c>
-      <c r="H86" s="1" t="s">
+      <c r="H86" t="s">
         <v>206</v>
       </c>
-      <c r="I86" s="1" t="s">
+      <c r="I86" t="s">
         <v>27</v>
       </c>
-      <c r="J86" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K86" s="1" t="s">
+      <c r="J86" t="s">
+        <v>23</v>
+      </c>
+      <c r="K86" t="s">
         <v>24</v>
       </c>
       <c r="L86">
@@ -7088,31 +7413,31 @@
       <c r="B87">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="C87" t="s">
         <v>18</v>
       </c>
-      <c r="D87" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E87" s="1" t="s">
+      <c r="D87" t="s">
+        <v>19</v>
+      </c>
+      <c r="E87" t="s">
         <v>207</v>
       </c>
       <c r="F87">
         <v>0</v>
       </c>
-      <c r="G87" s="2">
+      <c r="G87" s="1">
         <v>45582.224305555559</v>
       </c>
-      <c r="H87" s="1" t="s">
+      <c r="H87" t="s">
         <v>208</v>
       </c>
-      <c r="I87" s="1" t="s">
+      <c r="I87" t="s">
         <v>27</v>
       </c>
-      <c r="J87" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K87" s="1" t="s">
+      <c r="J87" t="s">
+        <v>23</v>
+      </c>
+      <c r="K87" t="s">
         <v>24</v>
       </c>
       <c r="L87">
@@ -7144,31 +7469,31 @@
       <c r="B88">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="C88" t="s">
         <v>18</v>
       </c>
-      <c r="D88" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E88" s="1" t="s">
+      <c r="D88" t="s">
+        <v>19</v>
+      </c>
+      <c r="E88" t="s">
         <v>209</v>
       </c>
       <c r="F88">
         <v>11</v>
       </c>
-      <c r="G88" s="2">
+      <c r="G88" s="1">
         <v>45582.988194444442</v>
       </c>
-      <c r="H88" s="1" t="s">
+      <c r="H88" t="s">
         <v>210</v>
       </c>
-      <c r="I88" s="1" t="s">
+      <c r="I88" t="s">
         <v>42</v>
       </c>
-      <c r="J88" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K88" s="1" t="s">
+      <c r="J88" t="s">
+        <v>23</v>
+      </c>
+      <c r="K88" t="s">
         <v>24</v>
       </c>
       <c r="L88">
@@ -7200,31 +7525,31 @@
       <c r="B89">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="C89" t="s">
         <v>18</v>
       </c>
-      <c r="D89" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E89" s="1" t="s">
+      <c r="D89" t="s">
+        <v>19</v>
+      </c>
+      <c r="E89" t="s">
         <v>211</v>
       </c>
       <c r="F89">
         <v>0</v>
       </c>
-      <c r="G89" s="2">
+      <c r="G89" s="1">
         <v>45585.992361111108</v>
       </c>
-      <c r="H89" s="1" t="s">
+      <c r="H89" t="s">
         <v>212</v>
       </c>
-      <c r="I89" s="1" t="s">
+      <c r="I89" t="s">
         <v>27</v>
       </c>
-      <c r="J89" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K89" s="1" t="s">
+      <c r="J89" t="s">
+        <v>23</v>
+      </c>
+      <c r="K89" t="s">
         <v>24</v>
       </c>
       <c r="L89">
@@ -7256,31 +7581,31 @@
       <c r="B90">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="C90" t="s">
         <v>18</v>
       </c>
-      <c r="D90" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E90" s="1" t="s">
+      <c r="D90" t="s">
+        <v>19</v>
+      </c>
+      <c r="E90" t="s">
         <v>213</v>
       </c>
       <c r="F90">
         <v>0</v>
       </c>
-      <c r="G90" s="2">
+      <c r="G90" s="1">
         <v>45588.109027777777</v>
       </c>
-      <c r="H90" s="1" t="s">
+      <c r="H90" t="s">
         <v>214</v>
       </c>
-      <c r="I90" s="1" t="s">
+      <c r="I90" t="s">
         <v>27</v>
       </c>
-      <c r="J90" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K90" s="1" t="s">
+      <c r="J90" t="s">
+        <v>23</v>
+      </c>
+      <c r="K90" t="s">
         <v>24</v>
       </c>
       <c r="L90">
@@ -7312,31 +7637,31 @@
       <c r="B91">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="C91" t="s">
         <v>18</v>
       </c>
-      <c r="D91" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E91" s="1" t="s">
+      <c r="D91" t="s">
+        <v>19</v>
+      </c>
+      <c r="E91" t="s">
         <v>215</v>
       </c>
       <c r="F91">
         <v>0</v>
       </c>
-      <c r="G91" s="2">
+      <c r="G91" s="1">
         <v>45589.98541666667</v>
       </c>
-      <c r="H91" s="1" t="s">
+      <c r="H91" t="s">
         <v>216</v>
       </c>
-      <c r="I91" s="1" t="s">
+      <c r="I91" t="s">
         <v>22</v>
       </c>
-      <c r="J91" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K91" s="1" t="s">
+      <c r="J91" t="s">
+        <v>23</v>
+      </c>
+      <c r="K91" t="s">
         <v>24</v>
       </c>
       <c r="L91">
@@ -7368,31 +7693,31 @@
       <c r="B92">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="C92" t="s">
         <v>18</v>
       </c>
-      <c r="D92" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E92" s="1" t="s">
+      <c r="D92" t="s">
+        <v>19</v>
+      </c>
+      <c r="E92" t="s">
         <v>217</v>
       </c>
       <c r="F92">
         <v>0</v>
       </c>
-      <c r="G92" s="2">
+      <c r="G92" s="1">
         <v>45593.321527777778</v>
       </c>
-      <c r="H92" s="1" t="s">
+      <c r="H92" t="s">
         <v>218</v>
       </c>
-      <c r="I92" s="1" t="s">
+      <c r="I92" t="s">
         <v>27</v>
       </c>
-      <c r="J92" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K92" s="1" t="s">
+      <c r="J92" t="s">
+        <v>23</v>
+      </c>
+      <c r="K92" t="s">
         <v>24</v>
       </c>
       <c r="L92">
@@ -7424,31 +7749,31 @@
       <c r="B93">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="C93" t="s">
         <v>18</v>
       </c>
-      <c r="D93" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E93" s="1" t="s">
+      <c r="D93" t="s">
+        <v>19</v>
+      </c>
+      <c r="E93" t="s">
         <v>219</v>
       </c>
       <c r="F93">
         <v>0</v>
       </c>
-      <c r="G93" s="2">
+      <c r="G93" s="1">
         <v>45604.163888888892</v>
       </c>
-      <c r="H93" s="1" t="s">
+      <c r="H93" t="s">
         <v>220</v>
       </c>
-      <c r="I93" s="1" t="s">
+      <c r="I93" t="s">
         <v>22</v>
       </c>
-      <c r="J93" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K93" s="1" t="s">
+      <c r="J93" t="s">
+        <v>23</v>
+      </c>
+      <c r="K93" t="s">
         <v>24</v>
       </c>
       <c r="L93">
@@ -7480,31 +7805,31 @@
       <c r="B94">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="C94" t="s">
         <v>18</v>
       </c>
-      <c r="D94" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E94" s="1" t="s">
+      <c r="D94" t="s">
+        <v>19</v>
+      </c>
+      <c r="E94" t="s">
         <v>221</v>
       </c>
       <c r="F94">
         <v>0</v>
       </c>
-      <c r="G94" s="2">
+      <c r="G94" s="1">
         <v>45607.032638888886</v>
       </c>
-      <c r="H94" s="1" t="s">
+      <c r="H94" t="s">
         <v>222</v>
       </c>
-      <c r="I94" s="1" t="s">
+      <c r="I94" t="s">
         <v>27</v>
       </c>
-      <c r="J94" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K94" s="1" t="s">
+      <c r="J94" t="s">
+        <v>23</v>
+      </c>
+      <c r="K94" t="s">
         <v>24</v>
       </c>
       <c r="L94">
@@ -7536,31 +7861,31 @@
       <c r="B95">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C95" s="1" t="s">
+      <c r="C95" t="s">
         <v>18</v>
       </c>
-      <c r="D95" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E95" s="1" t="s">
+      <c r="D95" t="s">
+        <v>19</v>
+      </c>
+      <c r="E95" t="s">
         <v>223</v>
       </c>
       <c r="F95">
         <v>53</v>
       </c>
-      <c r="G95" s="2">
+      <c r="G95" s="1">
         <v>45608.966666666667</v>
       </c>
-      <c r="H95" s="1" t="s">
+      <c r="H95" t="s">
         <v>224</v>
       </c>
-      <c r="I95" s="1" t="s">
+      <c r="I95" t="s">
         <v>42</v>
       </c>
-      <c r="J95" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K95" s="1" t="s">
+      <c r="J95" t="s">
+        <v>23</v>
+      </c>
+      <c r="K95" t="s">
         <v>24</v>
       </c>
       <c r="L95">
@@ -7592,31 +7917,31 @@
       <c r="B96">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="C96" t="s">
         <v>18</v>
       </c>
-      <c r="D96" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E96" s="1" t="s">
+      <c r="D96" t="s">
+        <v>19</v>
+      </c>
+      <c r="E96" t="s">
         <v>225</v>
       </c>
       <c r="F96">
         <v>86</v>
       </c>
-      <c r="G96" s="2">
+      <c r="G96" s="1">
         <v>45611.022222222222</v>
       </c>
-      <c r="H96" s="1" t="s">
+      <c r="H96" t="s">
         <v>226</v>
       </c>
-      <c r="I96" s="1" t="s">
+      <c r="I96" t="s">
         <v>42</v>
       </c>
-      <c r="J96" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K96" s="1" t="s">
+      <c r="J96" t="s">
+        <v>23</v>
+      </c>
+      <c r="K96" t="s">
         <v>24</v>
       </c>
       <c r="L96">
@@ -7648,31 +7973,31 @@
       <c r="B97">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C97" s="1" t="s">
+      <c r="C97" t="s">
         <v>18</v>
       </c>
-      <c r="D97" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E97" s="1" t="s">
+      <c r="D97" t="s">
+        <v>19</v>
+      </c>
+      <c r="E97" t="s">
         <v>227</v>
       </c>
       <c r="F97">
         <v>0</v>
       </c>
-      <c r="G97" s="2">
+      <c r="G97" s="1">
         <v>45615.098611111112</v>
       </c>
-      <c r="H97" s="1" t="s">
+      <c r="H97" t="s">
         <v>228</v>
       </c>
-      <c r="I97" s="1" t="s">
+      <c r="I97" t="s">
         <v>27</v>
       </c>
-      <c r="J97" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K97" s="1" t="s">
+      <c r="J97" t="s">
+        <v>23</v>
+      </c>
+      <c r="K97" t="s">
         <v>24</v>
       </c>
       <c r="L97">
@@ -7704,31 +8029,31 @@
       <c r="B98">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C98" s="1" t="s">
+      <c r="C98" t="s">
         <v>18</v>
       </c>
-      <c r="D98" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E98" s="1" t="s">
+      <c r="D98" t="s">
+        <v>19</v>
+      </c>
+      <c r="E98" t="s">
         <v>229</v>
       </c>
       <c r="F98">
         <v>0</v>
       </c>
-      <c r="G98" s="2">
+      <c r="G98" s="1">
         <v>45616.02847222222</v>
       </c>
-      <c r="H98" s="1" t="s">
+      <c r="H98" t="s">
         <v>230</v>
       </c>
-      <c r="I98" s="1" t="s">
+      <c r="I98" t="s">
         <v>27</v>
       </c>
-      <c r="J98" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K98" s="1" t="s">
+      <c r="J98" t="s">
+        <v>23</v>
+      </c>
+      <c r="K98" t="s">
         <v>24</v>
       </c>
       <c r="L98">
@@ -7760,31 +8085,31 @@
       <c r="B99">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C99" s="1" t="s">
+      <c r="C99" t="s">
         <v>18</v>
       </c>
-      <c r="D99" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E99" s="1" t="s">
+      <c r="D99" t="s">
+        <v>19</v>
+      </c>
+      <c r="E99" t="s">
         <v>231</v>
       </c>
       <c r="F99">
         <v>0</v>
       </c>
-      <c r="G99" s="2">
+      <c r="G99" s="1">
         <v>45616.980555555558</v>
       </c>
-      <c r="H99" s="1" t="s">
+      <c r="H99" t="s">
         <v>232</v>
       </c>
-      <c r="I99" s="1" t="s">
+      <c r="I99" t="s">
         <v>27</v>
       </c>
-      <c r="J99" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K99" s="1" t="s">
+      <c r="J99" t="s">
+        <v>23</v>
+      </c>
+      <c r="K99" t="s">
         <v>24</v>
       </c>
       <c r="L99">
@@ -7816,31 +8141,31 @@
       <c r="B100">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C100" s="1" t="s">
+      <c r="C100" t="s">
         <v>18</v>
       </c>
-      <c r="D100" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E100" s="1" t="s">
+      <c r="D100" t="s">
+        <v>19</v>
+      </c>
+      <c r="E100" t="s">
         <v>233</v>
       </c>
       <c r="F100">
         <v>0</v>
       </c>
-      <c r="G100" s="2">
+      <c r="G100" s="1">
         <v>45631.186805555553</v>
       </c>
-      <c r="H100" s="1" t="s">
+      <c r="H100" t="s">
         <v>234</v>
       </c>
-      <c r="I100" s="1" t="s">
+      <c r="I100" t="s">
         <v>27</v>
       </c>
-      <c r="J100" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K100" s="1" t="s">
+      <c r="J100" t="s">
+        <v>23</v>
+      </c>
+      <c r="K100" t="s">
         <v>24</v>
       </c>
       <c r="L100">
@@ -7872,31 +8197,31 @@
       <c r="B101">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C101" s="1" t="s">
+      <c r="C101" t="s">
         <v>18</v>
       </c>
-      <c r="D101" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E101" s="1" t="s">
+      <c r="D101" t="s">
+        <v>19</v>
+      </c>
+      <c r="E101" t="s">
         <v>235</v>
       </c>
       <c r="F101">
         <v>41</v>
       </c>
-      <c r="G101" s="2">
+      <c r="G101" s="1">
         <v>45632.213888888888</v>
       </c>
-      <c r="H101" s="1" t="s">
+      <c r="H101" t="s">
         <v>236</v>
       </c>
-      <c r="I101" s="1" t="s">
+      <c r="I101" t="s">
         <v>42</v>
       </c>
-      <c r="J101" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K101" s="1" t="s">
+      <c r="J101" t="s">
+        <v>23</v>
+      </c>
+      <c r="K101" t="s">
         <v>24</v>
       </c>
       <c r="L101">
@@ -7928,31 +8253,31 @@
       <c r="B102">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C102" s="1" t="s">
+      <c r="C102" t="s">
         <v>18</v>
       </c>
-      <c r="D102" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E102" s="1" t="s">
+      <c r="D102" t="s">
+        <v>19</v>
+      </c>
+      <c r="E102" t="s">
         <v>237</v>
       </c>
       <c r="F102">
         <v>0</v>
       </c>
-      <c r="G102" s="2">
+      <c r="G102" s="1">
         <v>45635.968055555553</v>
       </c>
-      <c r="H102" s="1" t="s">
+      <c r="H102" t="s">
         <v>238</v>
       </c>
-      <c r="I102" s="1" t="s">
+      <c r="I102" t="s">
         <v>27</v>
       </c>
-      <c r="J102" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K102" s="1" t="s">
+      <c r="J102" t="s">
+        <v>23</v>
+      </c>
+      <c r="K102" t="s">
         <v>24</v>
       </c>
       <c r="L102">
@@ -7984,31 +8309,31 @@
       <c r="B103">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C103" s="1" t="s">
+      <c r="C103" t="s">
         <v>18</v>
       </c>
-      <c r="D103" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E103" s="1" t="s">
+      <c r="D103" t="s">
+        <v>19</v>
+      </c>
+      <c r="E103" t="s">
         <v>239</v>
       </c>
       <c r="F103">
         <v>0</v>
       </c>
-      <c r="G103" s="2">
+      <c r="G103" s="1">
         <v>45644.023611111108</v>
       </c>
-      <c r="H103" s="1" t="s">
+      <c r="H103" t="s">
         <v>240</v>
       </c>
-      <c r="I103" s="1" t="s">
+      <c r="I103" t="s">
         <v>27</v>
       </c>
-      <c r="J103" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K103" s="1" t="s">
+      <c r="J103" t="s">
+        <v>23</v>
+      </c>
+      <c r="K103" t="s">
         <v>24</v>
       </c>
       <c r="L103">
@@ -8040,31 +8365,31 @@
       <c r="B104">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C104" s="1" t="s">
+      <c r="C104" t="s">
         <v>18</v>
       </c>
-      <c r="D104" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E104" s="1" t="s">
+      <c r="D104" t="s">
+        <v>19</v>
+      </c>
+      <c r="E104" t="s">
         <v>241</v>
       </c>
       <c r="F104">
         <v>32</v>
       </c>
-      <c r="G104" s="2">
+      <c r="G104" s="1">
         <v>45646.253472222219</v>
       </c>
-      <c r="H104" s="1" t="s">
+      <c r="H104" t="s">
         <v>242</v>
       </c>
-      <c r="I104" s="1" t="s">
+      <c r="I104" t="s">
         <v>42</v>
       </c>
-      <c r="J104" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K104" s="1" t="s">
+      <c r="J104" t="s">
+        <v>23</v>
+      </c>
+      <c r="K104" t="s">
         <v>24</v>
       </c>
       <c r="L104">
@@ -8096,31 +8421,31 @@
       <c r="B105">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C105" s="1" t="s">
+      <c r="C105" t="s">
         <v>18</v>
       </c>
-      <c r="D105" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E105" s="1" t="s">
+      <c r="D105" t="s">
+        <v>19</v>
+      </c>
+      <c r="E105" t="s">
         <v>243</v>
       </c>
       <c r="F105">
         <v>0</v>
       </c>
-      <c r="G105" s="2">
+      <c r="G105" s="1">
         <v>45648.990972222222</v>
       </c>
-      <c r="H105" s="1" t="s">
+      <c r="H105" t="s">
         <v>244</v>
       </c>
-      <c r="I105" s="1" t="s">
+      <c r="I105" t="s">
         <v>22</v>
       </c>
-      <c r="J105" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K105" s="1" t="s">
+      <c r="J105" t="s">
+        <v>23</v>
+      </c>
+      <c r="K105" t="s">
         <v>24</v>
       </c>
       <c r="L105">
@@ -8152,31 +8477,31 @@
       <c r="B106">
         <v>1.7841405312685856E+16</v>
       </c>
-      <c r="C106" s="1" t="s">
+      <c r="C106" t="s">
         <v>18</v>
       </c>
-      <c r="D106" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E106" s="1" t="s">
+      <c r="D106" t="s">
+        <v>19</v>
+      </c>
+      <c r="E106" t="s">
         <v>245</v>
       </c>
       <c r="F106">
         <v>0</v>
       </c>
-      <c r="G106" s="2">
+      <c r="G106" s="1">
         <v>45293.097222222219</v>
       </c>
-      <c r="H106" s="1" t="s">
+      <c r="H106" t="s">
         <v>246</v>
       </c>
-      <c r="I106" s="1" t="s">
+      <c r="I106" t="s">
         <v>27</v>
       </c>
-      <c r="J106" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K106" s="1" t="s">
+      <c r="J106" t="s">
+        <v>23</v>
+      </c>
+      <c r="K106" t="s">
         <v>24</v>
       </c>
       <c r="M106">
@@ -8205,29 +8530,28 @@
       <c r="B107">
         <v>100057565135049</v>
       </c>
-      <c r="C107" s="1"/>
-      <c r="D107" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E107" s="1" t="s">
+      <c r="D107" t="s">
+        <v>19</v>
+      </c>
+      <c r="E107" t="s">
         <v>249</v>
       </c>
       <c r="F107">
         <v>0</v>
       </c>
-      <c r="G107" s="2">
+      <c r="G107" s="1">
         <v>45648.98541666667</v>
       </c>
-      <c r="H107" s="1" t="s">
+      <c r="H107" t="s">
         <v>250</v>
       </c>
-      <c r="I107" s="1" t="s">
+      <c r="I107" t="s">
         <v>251</v>
       </c>
-      <c r="J107" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K107" s="1" t="s">
+      <c r="J107" t="s">
+        <v>23</v>
+      </c>
+      <c r="K107" t="s">
         <v>24</v>
       </c>
       <c r="L107">
@@ -8259,29 +8583,28 @@
       <c r="B108">
         <v>100057565135049</v>
       </c>
-      <c r="C108" s="1"/>
-      <c r="D108" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E108" s="1" t="s">
+      <c r="D108" t="s">
+        <v>19</v>
+      </c>
+      <c r="E108" t="s">
         <v>252</v>
       </c>
       <c r="F108">
         <v>0</v>
       </c>
-      <c r="G108" s="2">
+      <c r="G108" s="1">
         <v>45644.987500000003</v>
       </c>
-      <c r="H108" s="1" t="s">
+      <c r="H108" t="s">
         <v>253</v>
       </c>
-      <c r="I108" s="1" t="s">
+      <c r="I108" t="s">
         <v>254</v>
       </c>
-      <c r="J108" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K108" s="1" t="s">
+      <c r="J108" t="s">
+        <v>23</v>
+      </c>
+      <c r="K108" t="s">
         <v>24</v>
       </c>
       <c r="L108">
@@ -8313,29 +8636,28 @@
       <c r="B109">
         <v>100057565135049</v>
       </c>
-      <c r="C109" s="1"/>
-      <c r="D109" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E109" s="1" t="s">
+      <c r="D109" t="s">
+        <v>19</v>
+      </c>
+      <c r="E109" t="s">
         <v>255</v>
       </c>
       <c r="F109">
         <v>0</v>
       </c>
-      <c r="G109" s="2">
+      <c r="G109" s="1">
         <v>45642.04583333333</v>
       </c>
-      <c r="H109" s="1" t="s">
+      <c r="H109" t="s">
         <v>256</v>
       </c>
-      <c r="I109" s="1" t="s">
+      <c r="I109" t="s">
         <v>251</v>
       </c>
-      <c r="J109" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K109" s="1" t="s">
+      <c r="J109" t="s">
+        <v>23</v>
+      </c>
+      <c r="K109" t="s">
         <v>24</v>
       </c>
       <c r="L109">
@@ -8364,29 +8686,28 @@
       <c r="B110">
         <v>100057565135049</v>
       </c>
-      <c r="C110" s="1"/>
-      <c r="D110" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E110" s="1" t="s">
+      <c r="D110" t="s">
+        <v>19</v>
+      </c>
+      <c r="E110" t="s">
         <v>257</v>
       </c>
       <c r="F110">
         <v>0</v>
       </c>
-      <c r="G110" s="2">
+      <c r="G110" s="1">
         <v>45635.974305555559</v>
       </c>
-      <c r="H110" s="1" t="s">
+      <c r="H110" t="s">
         <v>258</v>
       </c>
-      <c r="I110" s="1" t="s">
+      <c r="I110" t="s">
         <v>251</v>
       </c>
-      <c r="J110" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K110" s="1" t="s">
+      <c r="J110" t="s">
+        <v>23</v>
+      </c>
+      <c r="K110" t="s">
         <v>24</v>
       </c>
       <c r="L110">
@@ -8418,29 +8739,28 @@
       <c r="B111">
         <v>100057565135049</v>
       </c>
-      <c r="C111" s="1"/>
-      <c r="D111" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E111" s="1" t="s">
+      <c r="D111" t="s">
+        <v>19</v>
+      </c>
+      <c r="E111" t="s">
         <v>259</v>
       </c>
       <c r="F111">
         <v>0</v>
       </c>
-      <c r="G111" s="2">
+      <c r="G111" s="1">
         <v>45631.193055555559</v>
       </c>
-      <c r="H111" s="1" t="s">
+      <c r="H111" t="s">
         <v>260</v>
       </c>
-      <c r="I111" s="1" t="s">
+      <c r="I111" t="s">
         <v>251</v>
       </c>
-      <c r="J111" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K111" s="1" t="s">
+      <c r="J111" t="s">
+        <v>23</v>
+      </c>
+      <c r="K111" t="s">
         <v>24</v>
       </c>
       <c r="L111">
@@ -8472,29 +8792,28 @@
       <c r="B112">
         <v>100057565135049</v>
       </c>
-      <c r="C112" s="1"/>
-      <c r="D112" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E112" s="1" t="s">
+      <c r="D112" t="s">
+        <v>19</v>
+      </c>
+      <c r="E112" t="s">
         <v>229</v>
       </c>
       <c r="F112">
         <v>0</v>
       </c>
-      <c r="G112" s="2">
+      <c r="G112" s="1">
         <v>45616.038194444445</v>
       </c>
-      <c r="H112" s="1" t="s">
+      <c r="H112" t="s">
         <v>261</v>
       </c>
-      <c r="I112" s="1" t="s">
+      <c r="I112" t="s">
         <v>251</v>
       </c>
-      <c r="J112" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K112" s="1" t="s">
+      <c r="J112" t="s">
+        <v>23</v>
+      </c>
+      <c r="K112" t="s">
         <v>24</v>
       </c>
       <c r="L112">
@@ -8526,29 +8845,28 @@
       <c r="B113">
         <v>100057565135049</v>
       </c>
-      <c r="C113" s="1"/>
-      <c r="D113" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E113" s="1" t="s">
+      <c r="D113" t="s">
+        <v>19</v>
+      </c>
+      <c r="E113" t="s">
         <v>262</v>
       </c>
       <c r="F113">
         <v>0</v>
       </c>
-      <c r="G113" s="2">
+      <c r="G113" s="1">
         <v>45615.073611111111</v>
       </c>
-      <c r="H113" s="1" t="s">
+      <c r="H113" t="s">
         <v>263</v>
       </c>
-      <c r="I113" s="1" t="s">
+      <c r="I113" t="s">
         <v>251</v>
       </c>
-      <c r="J113" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K113" s="1" t="s">
+      <c r="J113" t="s">
+        <v>23</v>
+      </c>
+      <c r="K113" t="s">
         <v>24</v>
       </c>
       <c r="L113">
@@ -8580,29 +8898,28 @@
       <c r="B114">
         <v>100057565135049</v>
       </c>
-      <c r="C114" s="1"/>
-      <c r="D114" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E114" s="1" t="s">
+      <c r="D114" t="s">
+        <v>19</v>
+      </c>
+      <c r="E114" t="s">
         <v>264</v>
       </c>
       <c r="F114">
         <v>86</v>
       </c>
-      <c r="G114" s="2">
+      <c r="G114" s="1">
         <v>45611.145138888889</v>
       </c>
-      <c r="H114" s="1" t="s">
+      <c r="H114" t="s">
         <v>265</v>
       </c>
-      <c r="I114" s="1" t="s">
+      <c r="I114" t="s">
         <v>266</v>
       </c>
-      <c r="J114" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K114" s="1" t="s">
+      <c r="J114" t="s">
+        <v>23</v>
+      </c>
+      <c r="K114" t="s">
         <v>24</v>
       </c>
       <c r="L114">
@@ -8634,29 +8951,28 @@
       <c r="B115">
         <v>100057565135049</v>
       </c>
-      <c r="C115" s="1"/>
-      <c r="D115" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E115" s="1" t="s">
+      <c r="D115" t="s">
+        <v>19</v>
+      </c>
+      <c r="E115" t="s">
         <v>267</v>
       </c>
       <c r="F115">
         <v>54</v>
       </c>
-      <c r="G115" s="2">
+      <c r="G115" s="1">
         <v>45608.964583333334</v>
       </c>
-      <c r="H115" s="1" t="s">
+      <c r="H115" t="s">
         <v>268</v>
       </c>
-      <c r="I115" s="1" t="s">
+      <c r="I115" t="s">
         <v>266</v>
       </c>
-      <c r="J115" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K115" s="1" t="s">
+      <c r="J115" t="s">
+        <v>23</v>
+      </c>
+      <c r="K115" t="s">
         <v>24</v>
       </c>
       <c r="L115">
@@ -8688,29 +9004,28 @@
       <c r="B116">
         <v>100057565135049</v>
       </c>
-      <c r="C116" s="1"/>
-      <c r="D116" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E116" s="1" t="s">
+      <c r="D116" t="s">
+        <v>19</v>
+      </c>
+      <c r="E116" t="s">
         <v>269</v>
       </c>
       <c r="F116">
         <v>0</v>
       </c>
-      <c r="G116" s="2">
+      <c r="G116" s="1">
         <v>45603.20208333333</v>
       </c>
-      <c r="H116" s="1" t="s">
+      <c r="H116" t="s">
         <v>270</v>
       </c>
-      <c r="I116" s="1" t="s">
+      <c r="I116" t="s">
         <v>271</v>
       </c>
-      <c r="J116" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K116" s="1" t="s">
+      <c r="J116" t="s">
+        <v>23</v>
+      </c>
+      <c r="K116" t="s">
         <v>24</v>
       </c>
     </row>
@@ -8721,29 +9036,28 @@
       <c r="B117">
         <v>100057565135049</v>
       </c>
-      <c r="C117" s="1"/>
-      <c r="D117" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E117" s="1" t="s">
+      <c r="D117" t="s">
+        <v>19</v>
+      </c>
+      <c r="E117" t="s">
         <v>272</v>
       </c>
       <c r="F117">
         <v>0</v>
       </c>
-      <c r="G117" s="2">
+      <c r="G117" s="1">
         <v>45589.993055555555</v>
       </c>
-      <c r="H117" s="1" t="s">
+      <c r="H117" t="s">
         <v>273</v>
       </c>
-      <c r="I117" s="1" t="s">
+      <c r="I117" t="s">
         <v>271</v>
       </c>
-      <c r="J117" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K117" s="1" t="s">
+      <c r="J117" t="s">
+        <v>23</v>
+      </c>
+      <c r="K117" t="s">
         <v>24</v>
       </c>
       <c r="L117">
@@ -8775,29 +9089,28 @@
       <c r="B118">
         <v>100057565135049</v>
       </c>
-      <c r="C118" s="1"/>
-      <c r="D118" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E118" s="1" t="s">
+      <c r="D118" t="s">
+        <v>19</v>
+      </c>
+      <c r="E118" t="s">
         <v>274</v>
       </c>
       <c r="F118">
         <v>0</v>
       </c>
-      <c r="G118" s="2">
+      <c r="G118" s="1">
         <v>45588.995833333334</v>
       </c>
-      <c r="H118" s="1" t="s">
+      <c r="H118" t="s">
         <v>275</v>
       </c>
-      <c r="I118" s="1" t="s">
+      <c r="I118" t="s">
         <v>251</v>
       </c>
-      <c r="J118" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K118" s="1" t="s">
+      <c r="J118" t="s">
+        <v>23</v>
+      </c>
+      <c r="K118" t="s">
         <v>24</v>
       </c>
       <c r="L118">
@@ -8829,29 +9142,28 @@
       <c r="B119">
         <v>100057565135049</v>
       </c>
-      <c r="C119" s="1"/>
-      <c r="D119" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E119" s="1" t="s">
+      <c r="D119" t="s">
+        <v>19</v>
+      </c>
+      <c r="E119" t="s">
         <v>276</v>
       </c>
       <c r="F119">
         <v>0</v>
       </c>
-      <c r="G119" s="2">
+      <c r="G119" s="1">
         <v>45583.012499999997</v>
       </c>
-      <c r="H119" s="1" t="s">
+      <c r="H119" t="s">
         <v>277</v>
       </c>
-      <c r="I119" s="1" t="s">
+      <c r="I119" t="s">
         <v>251</v>
       </c>
-      <c r="J119" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K119" s="1" t="s">
+      <c r="J119" t="s">
+        <v>23</v>
+      </c>
+      <c r="K119" t="s">
         <v>24</v>
       </c>
       <c r="L119">
@@ -8883,29 +9195,28 @@
       <c r="B120">
         <v>100057565135049</v>
       </c>
-      <c r="C120" s="1"/>
-      <c r="D120" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E120" s="1" t="s">
+      <c r="D120" t="s">
+        <v>19</v>
+      </c>
+      <c r="E120" t="s">
         <v>278</v>
       </c>
       <c r="F120">
         <v>93</v>
       </c>
-      <c r="G120" s="2">
+      <c r="G120" s="1">
         <v>45581.01666666667</v>
       </c>
-      <c r="H120" s="1" t="s">
+      <c r="H120" t="s">
         <v>279</v>
       </c>
-      <c r="I120" s="1" t="s">
+      <c r="I120" t="s">
         <v>266</v>
       </c>
-      <c r="J120" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K120" s="1" t="s">
+      <c r="J120" t="s">
+        <v>23</v>
+      </c>
+      <c r="K120" t="s">
         <v>24</v>
       </c>
       <c r="L120">
@@ -8937,29 +9248,28 @@
       <c r="B121">
         <v>100057565135049</v>
       </c>
-      <c r="C121" s="1"/>
-      <c r="D121" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E121" s="1" t="s">
+      <c r="D121" t="s">
+        <v>19</v>
+      </c>
+      <c r="E121" t="s">
         <v>280</v>
       </c>
       <c r="F121">
         <v>99</v>
       </c>
-      <c r="G121" s="2">
+      <c r="G121" s="1">
         <v>45579.116666666669</v>
       </c>
-      <c r="H121" s="1" t="s">
+      <c r="H121" t="s">
         <v>281</v>
       </c>
-      <c r="I121" s="1" t="s">
+      <c r="I121" t="s">
         <v>266</v>
       </c>
-      <c r="J121" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K121" s="1" t="s">
+      <c r="J121" t="s">
+        <v>23</v>
+      </c>
+      <c r="K121" t="s">
         <v>24</v>
       </c>
       <c r="L121">
@@ -8991,29 +9301,28 @@
       <c r="B122">
         <v>100057565135049</v>
       </c>
-      <c r="C122" s="1"/>
-      <c r="D122" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E122" s="1" t="s">
+      <c r="D122" t="s">
+        <v>19</v>
+      </c>
+      <c r="E122" t="s">
         <v>282</v>
       </c>
       <c r="F122">
         <v>26</v>
       </c>
-      <c r="G122" s="2">
+      <c r="G122" s="1">
         <v>45569.169444444444</v>
       </c>
-      <c r="H122" s="1" t="s">
+      <c r="H122" t="s">
         <v>283</v>
       </c>
-      <c r="I122" s="1" t="s">
+      <c r="I122" t="s">
         <v>266</v>
       </c>
-      <c r="J122" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K122" s="1" t="s">
+      <c r="J122" t="s">
+        <v>23</v>
+      </c>
+      <c r="K122" t="s">
         <v>24</v>
       </c>
       <c r="L122">
@@ -9045,29 +9354,28 @@
       <c r="B123">
         <v>100057565135049</v>
       </c>
-      <c r="C123" s="1"/>
-      <c r="D123" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E123" s="1" t="s">
+      <c r="D123" t="s">
+        <v>19</v>
+      </c>
+      <c r="E123" t="s">
         <v>284</v>
       </c>
       <c r="F123">
         <v>0</v>
       </c>
-      <c r="G123" s="2">
+      <c r="G123" s="1">
         <v>45566.28125</v>
       </c>
-      <c r="H123" s="1" t="s">
+      <c r="H123" t="s">
         <v>285</v>
       </c>
-      <c r="I123" s="1" t="s">
+      <c r="I123" t="s">
         <v>271</v>
       </c>
-      <c r="J123" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K123" s="1" t="s">
+      <c r="J123" t="s">
+        <v>23</v>
+      </c>
+      <c r="K123" t="s">
         <v>24</v>
       </c>
       <c r="L123">
@@ -9099,29 +9407,28 @@
       <c r="B124">
         <v>100057565135049</v>
       </c>
-      <c r="C124" s="1"/>
-      <c r="D124" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E124" s="1" t="s">
+      <c r="D124" t="s">
+        <v>19</v>
+      </c>
+      <c r="E124" t="s">
         <v>286</v>
       </c>
       <c r="F124">
         <v>0</v>
       </c>
-      <c r="G124" s="2">
+      <c r="G124" s="1">
         <v>45564.99722222222</v>
       </c>
-      <c r="H124" s="1" t="s">
+      <c r="H124" t="s">
         <v>287</v>
       </c>
-      <c r="I124" s="1" t="s">
+      <c r="I124" t="s">
         <v>251</v>
       </c>
-      <c r="J124" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K124" s="1" t="s">
+      <c r="J124" t="s">
+        <v>23</v>
+      </c>
+      <c r="K124" t="s">
         <v>24</v>
       </c>
       <c r="L124">
@@ -9153,29 +9460,28 @@
       <c r="B125">
         <v>100057565135049</v>
       </c>
-      <c r="C125" s="1"/>
-      <c r="D125" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E125" s="1" t="s">
+      <c r="D125" t="s">
+        <v>19</v>
+      </c>
+      <c r="E125" t="s">
         <v>288</v>
       </c>
       <c r="F125">
         <v>0</v>
       </c>
-      <c r="G125" s="2">
+      <c r="G125" s="1">
         <v>45554.988194444442</v>
       </c>
-      <c r="H125" s="1" t="s">
+      <c r="H125" t="s">
         <v>289</v>
       </c>
-      <c r="I125" s="1" t="s">
+      <c r="I125" t="s">
         <v>251</v>
       </c>
-      <c r="J125" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K125" s="1" t="s">
+      <c r="J125" t="s">
+        <v>23</v>
+      </c>
+      <c r="K125" t="s">
         <v>24</v>
       </c>
       <c r="M125">
@@ -9204,29 +9510,28 @@
       <c r="B126">
         <v>100057565135049</v>
       </c>
-      <c r="C126" s="1"/>
-      <c r="D126" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E126" s="1" t="s">
+      <c r="D126" t="s">
+        <v>19</v>
+      </c>
+      <c r="E126" t="s">
         <v>290</v>
       </c>
       <c r="F126">
         <v>0</v>
       </c>
-      <c r="G126" s="2">
+      <c r="G126" s="1">
         <v>45552.054861111108</v>
       </c>
-      <c r="H126" s="1" t="s">
+      <c r="H126" t="s">
         <v>291</v>
       </c>
-      <c r="I126" s="1" t="s">
+      <c r="I126" t="s">
         <v>251</v>
       </c>
-      <c r="J126" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K126" s="1" t="s">
+      <c r="J126" t="s">
+        <v>23</v>
+      </c>
+      <c r="K126" t="s">
         <v>24</v>
       </c>
       <c r="M126">
@@ -9255,29 +9560,28 @@
       <c r="B127">
         <v>100057565135049</v>
       </c>
-      <c r="C127" s="1"/>
-      <c r="D127" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E127" s="1" t="s">
+      <c r="D127" t="s">
+        <v>19</v>
+      </c>
+      <c r="E127" t="s">
         <v>292</v>
       </c>
       <c r="F127">
         <v>15</v>
       </c>
-      <c r="G127" s="2">
+      <c r="G127" s="1">
         <v>45551.149305555555</v>
       </c>
-      <c r="H127" s="1" t="s">
+      <c r="H127" t="s">
         <v>293</v>
       </c>
-      <c r="I127" s="1" t="s">
+      <c r="I127" t="s">
         <v>266</v>
       </c>
-      <c r="J127" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K127" s="1" t="s">
+      <c r="J127" t="s">
+        <v>23</v>
+      </c>
+      <c r="K127" t="s">
         <v>24</v>
       </c>
       <c r="M127">
@@ -9306,29 +9610,28 @@
       <c r="B128">
         <v>100057565135049</v>
       </c>
-      <c r="C128" s="1"/>
-      <c r="D128" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E128" s="1" t="s">
+      <c r="D128" t="s">
+        <v>19</v>
+      </c>
+      <c r="E128" t="s">
         <v>294</v>
       </c>
       <c r="F128">
         <v>0</v>
       </c>
-      <c r="G128" s="2">
+      <c r="G128" s="1">
         <v>45546.081944444442</v>
       </c>
-      <c r="H128" s="1" t="s">
+      <c r="H128" t="s">
         <v>295</v>
       </c>
-      <c r="I128" s="1" t="s">
+      <c r="I128" t="s">
         <v>271</v>
       </c>
-      <c r="J128" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K128" s="1" t="s">
+      <c r="J128" t="s">
+        <v>23</v>
+      </c>
+      <c r="K128" t="s">
         <v>24</v>
       </c>
     </row>
@@ -9339,29 +9642,28 @@
       <c r="B129">
         <v>100057565135049</v>
       </c>
-      <c r="C129" s="1"/>
-      <c r="D129" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E129" s="1" t="s">
+      <c r="D129" t="s">
+        <v>19</v>
+      </c>
+      <c r="E129" t="s">
         <v>296</v>
       </c>
       <c r="F129">
         <v>0</v>
       </c>
-      <c r="G129" s="2">
+      <c r="G129" s="1">
         <v>45546.039583333331</v>
       </c>
-      <c r="H129" s="1" t="s">
+      <c r="H129" t="s">
         <v>297</v>
       </c>
-      <c r="I129" s="1" t="s">
+      <c r="I129" t="s">
         <v>251</v>
       </c>
-      <c r="J129" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K129" s="1" t="s">
+      <c r="J129" t="s">
+        <v>23</v>
+      </c>
+      <c r="K129" t="s">
         <v>24</v>
       </c>
       <c r="M129">
@@ -9390,29 +9692,28 @@
       <c r="B130">
         <v>100057565135049</v>
       </c>
-      <c r="C130" s="1"/>
-      <c r="D130" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E130" s="1" t="s">
+      <c r="D130" t="s">
+        <v>19</v>
+      </c>
+      <c r="E130" t="s">
         <v>298</v>
       </c>
       <c r="F130">
         <v>0</v>
       </c>
-      <c r="G130" s="2">
+      <c r="G130" s="1">
         <v>45544.036805555559</v>
       </c>
-      <c r="H130" s="1" t="s">
+      <c r="H130" t="s">
         <v>299</v>
       </c>
-      <c r="I130" s="1" t="s">
+      <c r="I130" t="s">
         <v>251</v>
       </c>
-      <c r="J130" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K130" s="1" t="s">
+      <c r="J130" t="s">
+        <v>23</v>
+      </c>
+      <c r="K130" t="s">
         <v>24</v>
       </c>
       <c r="M130">
@@ -9441,29 +9742,28 @@
       <c r="B131">
         <v>100057565135049</v>
       </c>
-      <c r="C131" s="1"/>
-      <c r="D131" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E131" s="1" t="s">
+      <c r="D131" t="s">
+        <v>19</v>
+      </c>
+      <c r="E131" t="s">
         <v>300</v>
       </c>
       <c r="F131">
         <v>32</v>
       </c>
-      <c r="G131" s="2">
+      <c r="G131" s="1">
         <v>45534.009722222225</v>
       </c>
-      <c r="H131" s="1" t="s">
+      <c r="H131" t="s">
         <v>301</v>
       </c>
-      <c r="I131" s="1" t="s">
+      <c r="I131" t="s">
         <v>266</v>
       </c>
-      <c r="J131" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K131" s="1" t="s">
+      <c r="J131" t="s">
+        <v>23</v>
+      </c>
+      <c r="K131" t="s">
         <v>24</v>
       </c>
       <c r="M131">
@@ -9492,29 +9792,28 @@
       <c r="B132">
         <v>100057565135049</v>
       </c>
-      <c r="C132" s="1"/>
-      <c r="D132" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E132" s="1" t="s">
+      <c r="D132" t="s">
+        <v>19</v>
+      </c>
+      <c r="E132" t="s">
         <v>302</v>
       </c>
       <c r="F132">
         <v>26</v>
       </c>
-      <c r="G132" s="2">
+      <c r="G132" s="1">
         <v>45524.22152777778</v>
       </c>
-      <c r="H132" s="1" t="s">
+      <c r="H132" t="s">
         <v>303</v>
       </c>
-      <c r="I132" s="1" t="s">
+      <c r="I132" t="s">
         <v>266</v>
       </c>
-      <c r="J132" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K132" s="1" t="s">
+      <c r="J132" t="s">
+        <v>23</v>
+      </c>
+      <c r="K132" t="s">
         <v>24</v>
       </c>
       <c r="M132">
@@ -9543,29 +9842,28 @@
       <c r="B133">
         <v>100057565135049</v>
       </c>
-      <c r="C133" s="1"/>
-      <c r="D133" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E133" s="1" t="s">
+      <c r="D133" t="s">
+        <v>19</v>
+      </c>
+      <c r="E133" t="s">
         <v>23</v>
       </c>
       <c r="F133">
         <v>0</v>
       </c>
-      <c r="G133" s="2">
+      <c r="G133" s="1">
         <v>45520.960416666669</v>
       </c>
-      <c r="H133" s="1" t="s">
+      <c r="H133" t="s">
         <v>304</v>
       </c>
-      <c r="I133" s="1" t="s">
+      <c r="I133" t="s">
         <v>271</v>
       </c>
-      <c r="J133" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K133" s="1" t="s">
+      <c r="J133" t="s">
+        <v>23</v>
+      </c>
+      <c r="K133" t="s">
         <v>24</v>
       </c>
       <c r="M133">
@@ -9594,29 +9892,28 @@
       <c r="B134">
         <v>100057565135049</v>
       </c>
-      <c r="C134" s="1"/>
-      <c r="D134" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E134" s="1" t="s">
+      <c r="D134" t="s">
+        <v>19</v>
+      </c>
+      <c r="E134" t="s">
         <v>305</v>
       </c>
       <c r="F134">
         <v>11</v>
       </c>
-      <c r="G134" s="2">
+      <c r="G134" s="1">
         <v>45519.055555555555</v>
       </c>
-      <c r="H134" s="1" t="s">
+      <c r="H134" t="s">
         <v>306</v>
       </c>
-      <c r="I134" s="1" t="s">
+      <c r="I134" t="s">
         <v>266</v>
       </c>
-      <c r="J134" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K134" s="1" t="s">
+      <c r="J134" t="s">
+        <v>23</v>
+      </c>
+      <c r="K134" t="s">
         <v>24</v>
       </c>
       <c r="M134">
@@ -9645,29 +9942,28 @@
       <c r="B135">
         <v>100057565135049</v>
       </c>
-      <c r="C135" s="1"/>
-      <c r="D135" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E135" s="1" t="s">
+      <c r="D135" t="s">
+        <v>19</v>
+      </c>
+      <c r="E135" t="s">
         <v>307</v>
       </c>
       <c r="F135">
         <v>0</v>
       </c>
-      <c r="G135" s="2">
+      <c r="G135" s="1">
         <v>45474.25</v>
       </c>
-      <c r="H135" s="1" t="s">
+      <c r="H135" t="s">
         <v>308</v>
       </c>
-      <c r="I135" s="1" t="s">
+      <c r="I135" t="s">
         <v>251</v>
       </c>
-      <c r="J135" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K135" s="1" t="s">
+      <c r="J135" t="s">
+        <v>23</v>
+      </c>
+      <c r="K135" t="s">
         <v>24</v>
       </c>
       <c r="M135">
@@ -9696,29 +9992,28 @@
       <c r="B136">
         <v>100057565135049</v>
       </c>
-      <c r="C136" s="1"/>
-      <c r="D136" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E136" s="1" t="s">
+      <c r="D136" t="s">
+        <v>19</v>
+      </c>
+      <c r="E136" t="s">
         <v>309</v>
       </c>
       <c r="F136">
         <v>0</v>
       </c>
-      <c r="G136" s="2">
+      <c r="G136" s="1">
         <v>45463.003472222219</v>
       </c>
-      <c r="H136" s="1" t="s">
+      <c r="H136" t="s">
         <v>310</v>
       </c>
-      <c r="I136" s="1" t="s">
+      <c r="I136" t="s">
         <v>251</v>
       </c>
-      <c r="J136" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K136" s="1" t="s">
+      <c r="J136" t="s">
+        <v>23</v>
+      </c>
+      <c r="K136" t="s">
         <v>24</v>
       </c>
       <c r="M136">
@@ -9747,29 +10042,28 @@
       <c r="B137">
         <v>100057565135049</v>
       </c>
-      <c r="C137" s="1"/>
-      <c r="D137" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E137" s="1" t="s">
+      <c r="D137" t="s">
+        <v>19</v>
+      </c>
+      <c r="E137" t="s">
         <v>311</v>
       </c>
       <c r="F137">
         <v>26</v>
       </c>
-      <c r="G137" s="2">
+      <c r="G137" s="1">
         <v>45461.192361111112</v>
       </c>
-      <c r="H137" s="1" t="s">
+      <c r="H137" t="s">
         <v>312</v>
       </c>
-      <c r="I137" s="1" t="s">
+      <c r="I137" t="s">
         <v>266</v>
       </c>
-      <c r="J137" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K137" s="1" t="s">
+      <c r="J137" t="s">
+        <v>23</v>
+      </c>
+      <c r="K137" t="s">
         <v>24</v>
       </c>
       <c r="M137">
@@ -9798,29 +10092,28 @@
       <c r="B138">
         <v>100057565135049</v>
       </c>
-      <c r="C138" s="1"/>
-      <c r="D138" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E138" s="1" t="s">
+      <c r="D138" t="s">
+        <v>19</v>
+      </c>
+      <c r="E138" t="s">
         <v>313</v>
       </c>
       <c r="F138">
         <v>0</v>
       </c>
-      <c r="G138" s="2">
+      <c r="G138" s="1">
         <v>45460.331250000003</v>
       </c>
-      <c r="H138" s="1" t="s">
+      <c r="H138" t="s">
         <v>314</v>
       </c>
-      <c r="I138" s="1" t="s">
+      <c r="I138" t="s">
         <v>251</v>
       </c>
-      <c r="J138" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K138" s="1" t="s">
+      <c r="J138" t="s">
+        <v>23</v>
+      </c>
+      <c r="K138" t="s">
         <v>24</v>
       </c>
       <c r="M138">
@@ -9849,29 +10142,28 @@
       <c r="B139">
         <v>100057565135049</v>
       </c>
-      <c r="C139" s="1"/>
-      <c r="D139" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E139" s="1" t="s">
+      <c r="D139" t="s">
+        <v>19</v>
+      </c>
+      <c r="E139" t="s">
         <v>315</v>
       </c>
       <c r="F139">
         <v>0</v>
       </c>
-      <c r="G139" s="2">
+      <c r="G139" s="1">
         <v>45452.977083333331</v>
       </c>
-      <c r="H139" s="1" t="s">
+      <c r="H139" t="s">
         <v>316</v>
       </c>
-      <c r="I139" s="1" t="s">
+      <c r="I139" t="s">
         <v>251</v>
       </c>
-      <c r="J139" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K139" s="1" t="s">
+      <c r="J139" t="s">
+        <v>23</v>
+      </c>
+      <c r="K139" t="s">
         <v>24</v>
       </c>
       <c r="M139">
@@ -9900,29 +10192,28 @@
       <c r="B140">
         <v>100057565135049</v>
       </c>
-      <c r="C140" s="1"/>
-      <c r="D140" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E140" s="1" t="s">
+      <c r="D140" t="s">
+        <v>19</v>
+      </c>
+      <c r="E140" t="s">
         <v>317</v>
       </c>
       <c r="F140">
         <v>0</v>
       </c>
-      <c r="G140" s="2">
+      <c r="G140" s="1">
         <v>45440.155555555553</v>
       </c>
-      <c r="H140" s="1" t="s">
+      <c r="H140" t="s">
         <v>318</v>
       </c>
-      <c r="I140" s="1" t="s">
+      <c r="I140" t="s">
         <v>251</v>
       </c>
-      <c r="J140" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K140" s="1" t="s">
+      <c r="J140" t="s">
+        <v>23</v>
+      </c>
+      <c r="K140" t="s">
         <v>24</v>
       </c>
       <c r="M140">
@@ -9951,29 +10242,28 @@
       <c r="B141">
         <v>100057565135049</v>
       </c>
-      <c r="C141" s="1"/>
-      <c r="D141" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E141" s="1" t="s">
+      <c r="D141" t="s">
+        <v>19</v>
+      </c>
+      <c r="E141" t="s">
         <v>319</v>
       </c>
       <c r="F141">
         <v>0</v>
       </c>
-      <c r="G141" s="2">
+      <c r="G141" s="1">
         <v>45428.065972222219</v>
       </c>
-      <c r="H141" s="1" t="s">
+      <c r="H141" t="s">
         <v>320</v>
       </c>
-      <c r="I141" s="1" t="s">
+      <c r="I141" t="s">
         <v>271</v>
       </c>
-      <c r="J141" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K141" s="1" t="s">
+      <c r="J141" t="s">
+        <v>23</v>
+      </c>
+      <c r="K141" t="s">
         <v>24</v>
       </c>
       <c r="M141">
@@ -10002,29 +10292,28 @@
       <c r="B142">
         <v>100057565135049</v>
       </c>
-      <c r="C142" s="1"/>
-      <c r="D142" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E142" s="1" t="s">
+      <c r="D142" t="s">
+        <v>19</v>
+      </c>
+      <c r="E142" t="s">
         <v>321</v>
       </c>
       <c r="F142">
         <v>0</v>
       </c>
-      <c r="G142" s="2">
+      <c r="G142" s="1">
         <v>45426.20416666667</v>
       </c>
-      <c r="H142" s="1" t="s">
+      <c r="H142" t="s">
         <v>322</v>
       </c>
-      <c r="I142" s="1" t="s">
+      <c r="I142" t="s">
         <v>251</v>
       </c>
-      <c r="J142" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K142" s="1" t="s">
+      <c r="J142" t="s">
+        <v>23</v>
+      </c>
+      <c r="K142" t="s">
         <v>24</v>
       </c>
       <c r="M142">
@@ -10053,29 +10342,28 @@
       <c r="B143">
         <v>100057565135049</v>
       </c>
-      <c r="C143" s="1"/>
-      <c r="D143" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E143" s="1" t="s">
+      <c r="D143" t="s">
+        <v>19</v>
+      </c>
+      <c r="E143" t="s">
         <v>23</v>
       </c>
       <c r="F143">
         <v>0</v>
       </c>
-      <c r="G143" s="2">
+      <c r="G143" s="1">
         <v>45400.034722222219</v>
       </c>
-      <c r="H143" s="1" t="s">
+      <c r="H143" t="s">
         <v>323</v>
       </c>
-      <c r="I143" s="1" t="s">
+      <c r="I143" t="s">
         <v>266</v>
       </c>
-      <c r="J143" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K143" s="1" t="s">
+      <c r="J143" t="s">
+        <v>23</v>
+      </c>
+      <c r="K143" t="s">
         <v>24</v>
       </c>
       <c r="M143">
@@ -10104,29 +10392,28 @@
       <c r="B144">
         <v>100057565135049</v>
       </c>
-      <c r="C144" s="1"/>
-      <c r="D144" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E144" s="1" t="s">
+      <c r="D144" t="s">
+        <v>19</v>
+      </c>
+      <c r="E144" t="s">
         <v>23</v>
       </c>
       <c r="F144">
         <v>0</v>
       </c>
-      <c r="G144" s="2">
+      <c r="G144" s="1">
         <v>45397.98333333333</v>
       </c>
-      <c r="H144" s="1" t="s">
+      <c r="H144" t="s">
         <v>324</v>
       </c>
-      <c r="I144" s="1" t="s">
+      <c r="I144" t="s">
         <v>266</v>
       </c>
-      <c r="J144" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K144" s="1" t="s">
+      <c r="J144" t="s">
+        <v>23</v>
+      </c>
+      <c r="K144" t="s">
         <v>24</v>
       </c>
       <c r="M144">
@@ -10155,29 +10442,28 @@
       <c r="B145">
         <v>100057565135049</v>
       </c>
-      <c r="C145" s="1"/>
-      <c r="D145" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E145" s="1" t="s">
+      <c r="D145" t="s">
+        <v>19</v>
+      </c>
+      <c r="E145" t="s">
         <v>23</v>
       </c>
       <c r="F145">
         <v>0</v>
       </c>
-      <c r="G145" s="2">
+      <c r="G145" s="1">
         <v>45394.093055555553</v>
       </c>
-      <c r="H145" s="1" t="s">
+      <c r="H145" t="s">
         <v>325</v>
       </c>
-      <c r="I145" s="1" t="s">
+      <c r="I145" t="s">
         <v>254</v>
       </c>
-      <c r="J145" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K145" s="1" t="s">
+      <c r="J145" t="s">
+        <v>23</v>
+      </c>
+      <c r="K145" t="s">
         <v>24</v>
       </c>
       <c r="M145">
@@ -10203,29 +10489,28 @@
       <c r="B146">
         <v>100057565135049</v>
       </c>
-      <c r="C146" s="1"/>
-      <c r="D146" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E146" s="1" t="s">
+      <c r="D146" t="s">
+        <v>19</v>
+      </c>
+      <c r="E146" t="s">
         <v>326</v>
       </c>
       <c r="F146">
         <v>0</v>
       </c>
-      <c r="G146" s="2">
+      <c r="G146" s="1">
         <v>45384.008333333331</v>
       </c>
-      <c r="H146" s="1" t="s">
+      <c r="H146" t="s">
         <v>327</v>
       </c>
-      <c r="I146" s="1" t="s">
+      <c r="I146" t="s">
         <v>251</v>
       </c>
-      <c r="J146" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K146" s="1" t="s">
+      <c r="J146" t="s">
+        <v>23</v>
+      </c>
+      <c r="K146" t="s">
         <v>24</v>
       </c>
       <c r="M146">
@@ -10254,29 +10539,28 @@
       <c r="B147">
         <v>100057565135049</v>
       </c>
-      <c r="C147" s="1"/>
-      <c r="D147" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E147" s="1" t="s">
+      <c r="D147" t="s">
+        <v>19</v>
+      </c>
+      <c r="E147" t="s">
         <v>328</v>
       </c>
       <c r="F147">
         <v>0</v>
       </c>
-      <c r="G147" s="2">
+      <c r="G147" s="1">
         <v>45365.274305555555</v>
       </c>
-      <c r="H147" s="1" t="s">
+      <c r="H147" t="s">
         <v>329</v>
       </c>
-      <c r="I147" s="1" t="s">
+      <c r="I147" t="s">
         <v>251</v>
       </c>
-      <c r="J147" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K147" s="1" t="s">
+      <c r="J147" t="s">
+        <v>23</v>
+      </c>
+      <c r="K147" t="s">
         <v>24</v>
       </c>
       <c r="M147">
@@ -10302,29 +10586,28 @@
       <c r="B148">
         <v>100057565135049</v>
       </c>
-      <c r="C148" s="1"/>
-      <c r="D148" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E148" s="1" t="s">
+      <c r="D148" t="s">
+        <v>19</v>
+      </c>
+      <c r="E148" t="s">
         <v>330</v>
       </c>
       <c r="F148">
         <v>0</v>
       </c>
-      <c r="G148" s="2">
+      <c r="G148" s="1">
         <v>45357.277083333334</v>
       </c>
-      <c r="H148" s="1" t="s">
+      <c r="H148" t="s">
         <v>331</v>
       </c>
-      <c r="I148" s="1" t="s">
+      <c r="I148" t="s">
         <v>251</v>
       </c>
-      <c r="J148" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K148" s="1" t="s">
+      <c r="J148" t="s">
+        <v>23</v>
+      </c>
+      <c r="K148" t="s">
         <v>24</v>
       </c>
       <c r="M148">
@@ -10353,29 +10636,28 @@
       <c r="B149">
         <v>100057565135049</v>
       </c>
-      <c r="C149" s="1"/>
-      <c r="D149" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E149" s="1" t="s">
+      <c r="D149" t="s">
+        <v>19</v>
+      </c>
+      <c r="E149" t="s">
         <v>332</v>
       </c>
       <c r="F149">
         <v>0</v>
       </c>
-      <c r="G149" s="2">
+      <c r="G149" s="1">
         <v>45356.015972222223</v>
       </c>
-      <c r="H149" s="1" t="s">
+      <c r="H149" t="s">
         <v>333</v>
       </c>
-      <c r="I149" s="1" t="s">
+      <c r="I149" t="s">
         <v>251</v>
       </c>
-      <c r="J149" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K149" s="1" t="s">
+      <c r="J149" t="s">
+        <v>23</v>
+      </c>
+      <c r="K149" t="s">
         <v>24</v>
       </c>
       <c r="M149">
@@ -10401,29 +10683,28 @@
       <c r="B150">
         <v>100057565135049</v>
       </c>
-      <c r="C150" s="1"/>
-      <c r="D150" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E150" s="1" t="s">
+      <c r="D150" t="s">
+        <v>19</v>
+      </c>
+      <c r="E150" t="s">
         <v>334</v>
       </c>
       <c r="F150">
         <v>0</v>
       </c>
-      <c r="G150" s="2">
+      <c r="G150" s="1">
         <v>45351.004861111112</v>
       </c>
-      <c r="H150" s="1" t="s">
+      <c r="H150" t="s">
         <v>335</v>
       </c>
-      <c r="I150" s="1" t="s">
+      <c r="I150" t="s">
         <v>251</v>
       </c>
-      <c r="J150" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K150" s="1" t="s">
+      <c r="J150" t="s">
+        <v>23</v>
+      </c>
+      <c r="K150" t="s">
         <v>24</v>
       </c>
       <c r="M150">
@@ -10452,29 +10733,28 @@
       <c r="B151">
         <v>100057565135049</v>
       </c>
-      <c r="C151" s="1"/>
-      <c r="D151" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E151" s="1" t="s">
+      <c r="D151" t="s">
+        <v>19</v>
+      </c>
+      <c r="E151" t="s">
         <v>336</v>
       </c>
       <c r="F151">
         <v>0</v>
       </c>
-      <c r="G151" s="2">
+      <c r="G151" s="1">
         <v>45343.088194444441</v>
       </c>
-      <c r="H151" s="1" t="s">
+      <c r="H151" t="s">
         <v>337</v>
       </c>
-      <c r="I151" s="1" t="s">
+      <c r="I151" t="s">
         <v>251</v>
       </c>
-      <c r="J151" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K151" s="1" t="s">
+      <c r="J151" t="s">
+        <v>23</v>
+      </c>
+      <c r="K151" t="s">
         <v>24</v>
       </c>
       <c r="M151">
@@ -10500,29 +10780,28 @@
       <c r="B152">
         <v>100057565135049</v>
       </c>
-      <c r="C152" s="1"/>
-      <c r="D152" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E152" s="1" t="s">
+      <c r="D152" t="s">
+        <v>19</v>
+      </c>
+      <c r="E152" t="s">
         <v>338</v>
       </c>
       <c r="F152">
         <v>0</v>
       </c>
-      <c r="G152" s="2">
+      <c r="G152" s="1">
         <v>45336.070833333331</v>
       </c>
-      <c r="H152" s="1" t="s">
+      <c r="H152" t="s">
         <v>339</v>
       </c>
-      <c r="I152" s="1" t="s">
+      <c r="I152" t="s">
         <v>251</v>
       </c>
-      <c r="J152" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K152" s="1" t="s">
+      <c r="J152" t="s">
+        <v>23</v>
+      </c>
+      <c r="K152" t="s">
         <v>24</v>
       </c>
       <c r="M152">
@@ -10548,29 +10827,28 @@
       <c r="B153">
         <v>100057565135049</v>
       </c>
-      <c r="C153" s="1"/>
-      <c r="D153" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E153" s="1" t="s">
+      <c r="D153" t="s">
+        <v>19</v>
+      </c>
+      <c r="E153" t="s">
         <v>340</v>
       </c>
       <c r="F153">
         <v>0</v>
       </c>
-      <c r="G153" s="2">
+      <c r="G153" s="1">
         <v>45327.251388888886</v>
       </c>
-      <c r="H153" s="1" t="s">
+      <c r="H153" t="s">
         <v>341</v>
       </c>
-      <c r="I153" s="1" t="s">
+      <c r="I153" t="s">
         <v>251</v>
       </c>
-      <c r="J153" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K153" s="1" t="s">
+      <c r="J153" t="s">
+        <v>23</v>
+      </c>
+      <c r="K153" t="s">
         <v>24</v>
       </c>
       <c r="M153">
@@ -10596,29 +10874,28 @@
       <c r="B154">
         <v>100057565135049</v>
       </c>
-      <c r="C154" s="1"/>
-      <c r="D154" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E154" s="1" t="s">
+      <c r="D154" t="s">
+        <v>19</v>
+      </c>
+      <c r="E154" t="s">
         <v>342</v>
       </c>
       <c r="F154">
         <v>0</v>
       </c>
-      <c r="G154" s="2">
+      <c r="G154" s="1">
         <v>45313.260416666664</v>
       </c>
-      <c r="H154" s="1" t="s">
+      <c r="H154" t="s">
         <v>343</v>
       </c>
-      <c r="I154" s="1" t="s">
+      <c r="I154" t="s">
         <v>251</v>
       </c>
-      <c r="J154" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K154" s="1" t="s">
+      <c r="J154" t="s">
+        <v>23</v>
+      </c>
+      <c r="K154" t="s">
         <v>24</v>
       </c>
       <c r="M154">
@@ -10644,29 +10921,28 @@
       <c r="B155">
         <v>100057565135049</v>
       </c>
-      <c r="C155" s="1"/>
-      <c r="D155" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E155" s="1" t="s">
+      <c r="D155" t="s">
+        <v>19</v>
+      </c>
+      <c r="E155" t="s">
         <v>344</v>
       </c>
       <c r="F155">
         <v>0</v>
       </c>
-      <c r="G155" s="2">
+      <c r="G155" s="1">
         <v>45302.069444444445</v>
       </c>
-      <c r="H155" s="1" t="s">
+      <c r="H155" t="s">
         <v>345</v>
       </c>
-      <c r="I155" s="1" t="s">
+      <c r="I155" t="s">
         <v>251</v>
       </c>
-      <c r="J155" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K155" s="1" t="s">
+      <c r="J155" t="s">
+        <v>23</v>
+      </c>
+      <c r="K155" t="s">
         <v>24</v>
       </c>
       <c r="M155">
@@ -10692,29 +10968,28 @@
       <c r="B156">
         <v>100057565135049</v>
       </c>
-      <c r="C156" s="1"/>
-      <c r="D156" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E156" s="1" t="s">
+      <c r="D156" t="s">
+        <v>19</v>
+      </c>
+      <c r="E156" t="s">
         <v>346</v>
       </c>
       <c r="F156">
         <v>0</v>
       </c>
-      <c r="G156" s="2">
+      <c r="G156" s="1">
         <v>46013.168749999997</v>
       </c>
-      <c r="H156" s="1" t="s">
+      <c r="H156" t="s">
         <v>347</v>
       </c>
-      <c r="I156" s="1" t="s">
+      <c r="I156" t="s">
         <v>251</v>
       </c>
-      <c r="J156" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K156" s="1" t="s">
+      <c r="J156" t="s">
+        <v>23</v>
+      </c>
+      <c r="K156" t="s">
         <v>24</v>
       </c>
       <c r="L156">
@@ -10746,29 +11021,28 @@
       <c r="B157">
         <v>100057565135049</v>
       </c>
-      <c r="C157" s="1"/>
-      <c r="D157" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E157" s="1" t="s">
+      <c r="D157" t="s">
+        <v>19</v>
+      </c>
+      <c r="E157" t="s">
         <v>348</v>
       </c>
       <c r="F157">
         <v>0</v>
       </c>
-      <c r="G157" s="2">
+      <c r="G157" s="1">
         <v>45993.052083333336</v>
       </c>
-      <c r="H157" s="1" t="s">
+      <c r="H157" t="s">
         <v>349</v>
       </c>
-      <c r="I157" s="1" t="s">
+      <c r="I157" t="s">
         <v>254</v>
       </c>
-      <c r="J157" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K157" s="1" t="s">
+      <c r="J157" t="s">
+        <v>23</v>
+      </c>
+      <c r="K157" t="s">
         <v>24</v>
       </c>
       <c r="L157">
@@ -10800,29 +11074,28 @@
       <c r="B158">
         <v>100057565135049</v>
       </c>
-      <c r="C158" s="1"/>
-      <c r="D158" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E158" s="1" t="s">
+      <c r="D158" t="s">
+        <v>19</v>
+      </c>
+      <c r="E158" t="s">
         <v>350</v>
       </c>
       <c r="F158">
         <v>25</v>
       </c>
-      <c r="G158" s="2">
+      <c r="G158" s="1">
         <v>45991.990972222222</v>
       </c>
-      <c r="H158" s="1" t="s">
+      <c r="H158" t="s">
         <v>351</v>
       </c>
-      <c r="I158" s="1" t="s">
+      <c r="I158" t="s">
         <v>266</v>
       </c>
-      <c r="J158" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K158" s="1" t="s">
+      <c r="J158" t="s">
+        <v>23</v>
+      </c>
+      <c r="K158" t="s">
         <v>24</v>
       </c>
       <c r="L158">
@@ -10854,29 +11127,28 @@
       <c r="B159">
         <v>100057565135049</v>
       </c>
-      <c r="C159" s="1"/>
-      <c r="D159" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E159" s="1" t="s">
+      <c r="D159" t="s">
+        <v>19</v>
+      </c>
+      <c r="E159" t="s">
         <v>352</v>
       </c>
       <c r="F159">
         <v>0</v>
       </c>
-      <c r="G159" s="2">
+      <c r="G159" s="1">
         <v>45979.07708333333</v>
       </c>
-      <c r="H159" s="1" t="s">
+      <c r="H159" t="s">
         <v>353</v>
       </c>
-      <c r="I159" s="1" t="s">
+      <c r="I159" t="s">
         <v>251</v>
       </c>
-      <c r="J159" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K159" s="1" t="s">
+      <c r="J159" t="s">
+        <v>23</v>
+      </c>
+      <c r="K159" t="s">
         <v>24</v>
       </c>
       <c r="L159">
@@ -10908,29 +11180,28 @@
       <c r="B160">
         <v>100057565135049</v>
       </c>
-      <c r="C160" s="1"/>
-      <c r="D160" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E160" s="1" t="s">
+      <c r="D160" t="s">
+        <v>19</v>
+      </c>
+      <c r="E160" t="s">
         <v>354</v>
       </c>
       <c r="F160">
         <v>0</v>
       </c>
-      <c r="G160" s="2">
+      <c r="G160" s="1">
         <v>45946.912499999999</v>
       </c>
-      <c r="H160" s="1" t="s">
+      <c r="H160" t="s">
         <v>355</v>
       </c>
-      <c r="I160" s="1" t="s">
+      <c r="I160" t="s">
         <v>266</v>
       </c>
-      <c r="J160" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K160" s="1" t="s">
+      <c r="J160" t="s">
+        <v>23</v>
+      </c>
+      <c r="K160" t="s">
         <v>24</v>
       </c>
       <c r="L160">
@@ -10962,29 +11233,28 @@
       <c r="B161">
         <v>100057565135049</v>
       </c>
-      <c r="C161" s="1"/>
-      <c r="D161" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E161" s="1" t="s">
+      <c r="D161" t="s">
+        <v>19</v>
+      </c>
+      <c r="E161" t="s">
         <v>356</v>
       </c>
       <c r="F161">
         <v>0</v>
       </c>
-      <c r="G161" s="2">
+      <c r="G161" s="1">
         <v>45945.964583333334</v>
       </c>
-      <c r="H161" s="1" t="s">
+      <c r="H161" t="s">
         <v>357</v>
       </c>
-      <c r="I161" s="1" t="s">
+      <c r="I161" t="s">
         <v>251</v>
       </c>
-      <c r="J161" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K161" s="1" t="s">
+      <c r="J161" t="s">
+        <v>23</v>
+      </c>
+      <c r="K161" t="s">
         <v>24</v>
       </c>
       <c r="L161">
@@ -11016,29 +11286,28 @@
       <c r="B162">
         <v>100057565135049</v>
       </c>
-      <c r="C162" s="1"/>
-      <c r="D162" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E162" s="1" t="s">
+      <c r="D162" t="s">
+        <v>19</v>
+      </c>
+      <c r="E162" t="s">
         <v>358</v>
       </c>
       <c r="F162">
         <v>0</v>
       </c>
-      <c r="G162" s="2">
+      <c r="G162" s="1">
         <v>45944.986111111109</v>
       </c>
-      <c r="H162" s="1" t="s">
+      <c r="H162" t="s">
         <v>359</v>
       </c>
-      <c r="I162" s="1" t="s">
+      <c r="I162" t="s">
         <v>251</v>
       </c>
-      <c r="J162" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K162" s="1" t="s">
+      <c r="J162" t="s">
+        <v>23</v>
+      </c>
+      <c r="K162" t="s">
         <v>24</v>
       </c>
       <c r="L162">
@@ -11070,29 +11339,28 @@
       <c r="B163">
         <v>100057565135049</v>
       </c>
-      <c r="C163" s="1"/>
-      <c r="D163" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E163" s="1" t="s">
+      <c r="D163" t="s">
+        <v>19</v>
+      </c>
+      <c r="E163" t="s">
         <v>360</v>
       </c>
       <c r="F163">
         <v>0</v>
       </c>
-      <c r="G163" s="2">
+      <c r="G163" s="1">
         <v>45943.220138888886</v>
       </c>
-      <c r="H163" s="1" t="s">
+      <c r="H163" t="s">
         <v>361</v>
       </c>
-      <c r="I163" s="1" t="s">
+      <c r="I163" t="s">
         <v>251</v>
       </c>
-      <c r="J163" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K163" s="1" t="s">
+      <c r="J163" t="s">
+        <v>23</v>
+      </c>
+      <c r="K163" t="s">
         <v>24</v>
       </c>
       <c r="L163">
@@ -11124,29 +11392,28 @@
       <c r="B164">
         <v>100057565135049</v>
       </c>
-      <c r="C164" s="1"/>
-      <c r="D164" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E164" s="1" t="s">
+      <c r="D164" t="s">
+        <v>19</v>
+      </c>
+      <c r="E164" t="s">
         <v>362</v>
       </c>
       <c r="F164">
         <v>0</v>
       </c>
-      <c r="G164" s="2">
+      <c r="G164" s="1">
         <v>45940.065972222219</v>
       </c>
-      <c r="H164" s="1" t="s">
+      <c r="H164" t="s">
         <v>363</v>
       </c>
-      <c r="I164" s="1" t="s">
+      <c r="I164" t="s">
         <v>251</v>
       </c>
-      <c r="J164" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K164" s="1" t="s">
+      <c r="J164" t="s">
+        <v>23</v>
+      </c>
+      <c r="K164" t="s">
         <v>24</v>
       </c>
       <c r="L164">
@@ -11178,29 +11445,28 @@
       <c r="B165">
         <v>100057565135049</v>
       </c>
-      <c r="C165" s="1"/>
-      <c r="D165" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E165" s="1" t="s">
+      <c r="D165" t="s">
+        <v>19</v>
+      </c>
+      <c r="E165" t="s">
         <v>364</v>
       </c>
       <c r="F165">
         <v>0</v>
       </c>
-      <c r="G165" s="2">
+      <c r="G165" s="1">
         <v>45926.009027777778</v>
       </c>
-      <c r="H165" s="1" t="s">
+      <c r="H165" t="s">
         <v>365</v>
       </c>
-      <c r="I165" s="1" t="s">
+      <c r="I165" t="s">
         <v>251</v>
       </c>
-      <c r="J165" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K165" s="1" t="s">
+      <c r="J165" t="s">
+        <v>23</v>
+      </c>
+      <c r="K165" t="s">
         <v>24</v>
       </c>
       <c r="L165">
@@ -11232,29 +11498,28 @@
       <c r="B166">
         <v>100057565135049</v>
       </c>
-      <c r="C166" s="1"/>
-      <c r="D166" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E166" s="1" t="s">
+      <c r="D166" t="s">
+        <v>19</v>
+      </c>
+      <c r="E166" t="s">
         <v>366</v>
       </c>
       <c r="F166">
         <v>0</v>
       </c>
-      <c r="G166" s="2">
+      <c r="G166" s="1">
         <v>45924.21875</v>
       </c>
-      <c r="H166" s="1" t="s">
+      <c r="H166" t="s">
         <v>367</v>
       </c>
-      <c r="I166" s="1" t="s">
+      <c r="I166" t="s">
         <v>254</v>
       </c>
-      <c r="J166" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K166" s="1" t="s">
+      <c r="J166" t="s">
+        <v>23</v>
+      </c>
+      <c r="K166" t="s">
         <v>24</v>
       </c>
       <c r="L166">
@@ -11286,29 +11551,28 @@
       <c r="B167">
         <v>100057565135049</v>
       </c>
-      <c r="C167" s="1"/>
-      <c r="D167" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E167" s="1" t="s">
+      <c r="D167" t="s">
+        <v>19</v>
+      </c>
+      <c r="E167" t="s">
         <v>368</v>
       </c>
       <c r="F167">
         <v>0</v>
       </c>
-      <c r="G167" s="2">
+      <c r="G167" s="1">
         <v>45923.099305555559</v>
       </c>
-      <c r="H167" s="1" t="s">
+      <c r="H167" t="s">
         <v>369</v>
       </c>
-      <c r="I167" s="1" t="s">
+      <c r="I167" t="s">
         <v>251</v>
       </c>
-      <c r="J167" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K167" s="1" t="s">
+      <c r="J167" t="s">
+        <v>23</v>
+      </c>
+      <c r="K167" t="s">
         <v>24</v>
       </c>
       <c r="L167">
@@ -11340,29 +11604,28 @@
       <c r="B168">
         <v>100057565135049</v>
       </c>
-      <c r="C168" s="1"/>
-      <c r="D168" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E168" s="1" t="s">
+      <c r="D168" t="s">
+        <v>19</v>
+      </c>
+      <c r="E168" t="s">
         <v>370</v>
       </c>
       <c r="F168">
         <v>0</v>
       </c>
-      <c r="G168" s="2">
+      <c r="G168" s="1">
         <v>45918.172222222223</v>
       </c>
-      <c r="H168" s="1" t="s">
+      <c r="H168" t="s">
         <v>371</v>
       </c>
-      <c r="I168" s="1" t="s">
+      <c r="I168" t="s">
         <v>251</v>
       </c>
-      <c r="J168" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K168" s="1" t="s">
+      <c r="J168" t="s">
+        <v>23</v>
+      </c>
+      <c r="K168" t="s">
         <v>24</v>
       </c>
       <c r="L168">
@@ -11394,29 +11657,28 @@
       <c r="B169">
         <v>100057565135049</v>
       </c>
-      <c r="C169" s="1"/>
-      <c r="D169" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E169" s="1" t="s">
+      <c r="D169" t="s">
+        <v>19</v>
+      </c>
+      <c r="E169" t="s">
         <v>65</v>
       </c>
       <c r="F169">
         <v>0</v>
       </c>
-      <c r="G169" s="2">
+      <c r="G169" s="1">
         <v>45917.250694444447</v>
       </c>
-      <c r="H169" s="1" t="s">
+      <c r="H169" t="s">
         <v>372</v>
       </c>
-      <c r="I169" s="1" t="s">
+      <c r="I169" t="s">
         <v>251</v>
       </c>
-      <c r="J169" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K169" s="1" t="s">
+      <c r="J169" t="s">
+        <v>23</v>
+      </c>
+      <c r="K169" t="s">
         <v>24</v>
       </c>
       <c r="L169">
@@ -11448,29 +11710,28 @@
       <c r="B170">
         <v>100057565135049</v>
       </c>
-      <c r="C170" s="1"/>
-      <c r="D170" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E170" s="1" t="s">
+      <c r="D170" t="s">
+        <v>19</v>
+      </c>
+      <c r="E170" t="s">
         <v>373</v>
       </c>
       <c r="F170">
         <v>0</v>
       </c>
-      <c r="G170" s="2">
+      <c r="G170" s="1">
         <v>45917.161805555559</v>
       </c>
-      <c r="H170" s="1" t="s">
+      <c r="H170" t="s">
         <v>374</v>
       </c>
-      <c r="I170" s="1" t="s">
+      <c r="I170" t="s">
         <v>254</v>
       </c>
-      <c r="J170" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K170" s="1" t="s">
+      <c r="J170" t="s">
+        <v>23</v>
+      </c>
+      <c r="K170" t="s">
         <v>24</v>
       </c>
       <c r="L170">
@@ -11502,29 +11763,28 @@
       <c r="B171">
         <v>100057565135049</v>
       </c>
-      <c r="C171" s="1"/>
-      <c r="D171" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E171" s="1" t="s">
+      <c r="D171" t="s">
+        <v>19</v>
+      </c>
+      <c r="E171" t="s">
         <v>375</v>
       </c>
       <c r="F171">
         <v>0</v>
       </c>
-      <c r="G171" s="2">
+      <c r="G171" s="1">
         <v>45910.074305555558</v>
       </c>
-      <c r="H171" s="1" t="s">
+      <c r="H171" t="s">
         <v>376</v>
       </c>
-      <c r="I171" s="1" t="s">
+      <c r="I171" t="s">
         <v>251</v>
       </c>
-      <c r="J171" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K171" s="1" t="s">
+      <c r="J171" t="s">
+        <v>23</v>
+      </c>
+      <c r="K171" t="s">
         <v>24</v>
       </c>
       <c r="L171">
@@ -11556,29 +11816,28 @@
       <c r="B172">
         <v>100057565135049</v>
       </c>
-      <c r="C172" s="1"/>
-      <c r="D172" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E172" s="1" t="s">
+      <c r="D172" t="s">
+        <v>19</v>
+      </c>
+      <c r="E172" t="s">
         <v>377</v>
       </c>
       <c r="F172">
         <v>0</v>
       </c>
-      <c r="G172" s="2">
+      <c r="G172" s="1">
         <v>45908.018055555556</v>
       </c>
-      <c r="H172" s="1" t="s">
+      <c r="H172" t="s">
         <v>378</v>
       </c>
-      <c r="I172" s="1" t="s">
+      <c r="I172" t="s">
         <v>271</v>
       </c>
-      <c r="J172" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K172" s="1" t="s">
+      <c r="J172" t="s">
+        <v>23</v>
+      </c>
+      <c r="K172" t="s">
         <v>24</v>
       </c>
     </row>
@@ -11589,29 +11848,28 @@
       <c r="B173">
         <v>100057565135049</v>
       </c>
-      <c r="C173" s="1"/>
-      <c r="D173" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E173" s="1" t="s">
+      <c r="D173" t="s">
+        <v>19</v>
+      </c>
+      <c r="E173" t="s">
         <v>379</v>
       </c>
       <c r="F173">
         <v>0</v>
       </c>
-      <c r="G173" s="2">
+      <c r="G173" s="1">
         <v>45901.072916666664</v>
       </c>
-      <c r="H173" s="1" t="s">
+      <c r="H173" t="s">
         <v>380</v>
       </c>
-      <c r="I173" s="1" t="s">
+      <c r="I173" t="s">
         <v>251</v>
       </c>
-      <c r="J173" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K173" s="1" t="s">
+      <c r="J173" t="s">
+        <v>23</v>
+      </c>
+      <c r="K173" t="s">
         <v>24</v>
       </c>
       <c r="L173">
@@ -11643,29 +11901,28 @@
       <c r="B174">
         <v>100057565135049</v>
       </c>
-      <c r="C174" s="1"/>
-      <c r="D174" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E174" s="1" t="s">
+      <c r="D174" t="s">
+        <v>19</v>
+      </c>
+      <c r="E174" t="s">
         <v>87</v>
       </c>
       <c r="F174">
         <v>0</v>
       </c>
-      <c r="G174" s="2">
+      <c r="G174" s="1">
         <v>45898.099305555559</v>
       </c>
-      <c r="H174" s="1" t="s">
+      <c r="H174" t="s">
         <v>381</v>
       </c>
-      <c r="I174" s="1" t="s">
+      <c r="I174" t="s">
         <v>251</v>
       </c>
-      <c r="J174" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K174" s="1" t="s">
+      <c r="J174" t="s">
+        <v>23</v>
+      </c>
+      <c r="K174" t="s">
         <v>24</v>
       </c>
       <c r="L174">
@@ -11697,29 +11954,28 @@
       <c r="B175">
         <v>100057565135049</v>
       </c>
-      <c r="C175" s="1"/>
-      <c r="D175" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E175" s="1" t="s">
+      <c r="D175" t="s">
+        <v>19</v>
+      </c>
+      <c r="E175" t="s">
         <v>382</v>
       </c>
       <c r="F175">
         <v>0</v>
       </c>
-      <c r="G175" s="2">
+      <c r="G175" s="1">
         <v>45894.974999999999</v>
       </c>
-      <c r="H175" s="1" t="s">
+      <c r="H175" t="s">
         <v>383</v>
       </c>
-      <c r="I175" s="1" t="s">
+      <c r="I175" t="s">
         <v>251</v>
       </c>
-      <c r="J175" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K175" s="1" t="s">
+      <c r="J175" t="s">
+        <v>23</v>
+      </c>
+      <c r="K175" t="s">
         <v>24</v>
       </c>
       <c r="L175">
@@ -11751,29 +12007,28 @@
       <c r="B176">
         <v>100057565135049</v>
       </c>
-      <c r="C176" s="1"/>
-      <c r="D176" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E176" s="1" t="s">
+      <c r="D176" t="s">
+        <v>19</v>
+      </c>
+      <c r="E176" t="s">
         <v>384</v>
       </c>
       <c r="F176">
         <v>0</v>
       </c>
-      <c r="G176" s="2">
+      <c r="G176" s="1">
         <v>45827.069444444445</v>
       </c>
-      <c r="H176" s="1" t="s">
+      <c r="H176" t="s">
         <v>385</v>
       </c>
-      <c r="I176" s="1" t="s">
+      <c r="I176" t="s">
         <v>251</v>
       </c>
-      <c r="J176" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K176" s="1" t="s">
+      <c r="J176" t="s">
+        <v>23</v>
+      </c>
+      <c r="K176" t="s">
         <v>24</v>
       </c>
       <c r="L176">
@@ -11805,29 +12060,28 @@
       <c r="B177">
         <v>100057565135049</v>
       </c>
-      <c r="C177" s="1"/>
-      <c r="D177" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E177" s="1" t="s">
+      <c r="D177" t="s">
+        <v>19</v>
+      </c>
+      <c r="E177" t="s">
         <v>386</v>
       </c>
       <c r="F177">
         <v>0</v>
       </c>
-      <c r="G177" s="2">
+      <c r="G177" s="1">
         <v>45781.993055555555</v>
       </c>
-      <c r="H177" s="1" t="s">
+      <c r="H177" t="s">
         <v>387</v>
       </c>
-      <c r="I177" s="1" t="s">
+      <c r="I177" t="s">
         <v>251</v>
       </c>
-      <c r="J177" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K177" s="1" t="s">
+      <c r="J177" t="s">
+        <v>23</v>
+      </c>
+      <c r="K177" t="s">
         <v>24</v>
       </c>
       <c r="L177">
@@ -11859,29 +12113,28 @@
       <c r="B178">
         <v>100057565135049</v>
       </c>
-      <c r="C178" s="1"/>
-      <c r="D178" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E178" s="1" t="s">
+      <c r="D178" t="s">
+        <v>19</v>
+      </c>
+      <c r="E178" t="s">
         <v>388</v>
       </c>
       <c r="F178">
         <v>125</v>
       </c>
-      <c r="G178" s="2">
+      <c r="G178" s="1">
         <v>45776.001388888886</v>
       </c>
-      <c r="H178" s="1" t="s">
+      <c r="H178" t="s">
         <v>389</v>
       </c>
-      <c r="I178" s="1" t="s">
+      <c r="I178" t="s">
         <v>266</v>
       </c>
-      <c r="J178" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K178" s="1" t="s">
+      <c r="J178" t="s">
+        <v>23</v>
+      </c>
+      <c r="K178" t="s">
         <v>24</v>
       </c>
       <c r="L178">
@@ -11913,29 +12166,28 @@
       <c r="B179">
         <v>100057565135049</v>
       </c>
-      <c r="C179" s="1"/>
-      <c r="D179" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E179" s="1" t="s">
+      <c r="D179" t="s">
+        <v>19</v>
+      </c>
+      <c r="E179" t="s">
         <v>390</v>
       </c>
       <c r="F179">
         <v>0</v>
       </c>
-      <c r="G179" s="2">
+      <c r="G179" s="1">
         <v>45774.984722222223</v>
       </c>
-      <c r="H179" s="1" t="s">
+      <c r="H179" t="s">
         <v>391</v>
       </c>
-      <c r="I179" s="1" t="s">
+      <c r="I179" t="s">
         <v>251</v>
       </c>
-      <c r="J179" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K179" s="1" t="s">
+      <c r="J179" t="s">
+        <v>23</v>
+      </c>
+      <c r="K179" t="s">
         <v>24</v>
       </c>
       <c r="L179">
@@ -11967,29 +12219,28 @@
       <c r="B180">
         <v>100057565135049</v>
       </c>
-      <c r="C180" s="1"/>
-      <c r="D180" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E180" s="1" t="s">
+      <c r="D180" t="s">
+        <v>19</v>
+      </c>
+      <c r="E180" t="s">
         <v>392</v>
       </c>
       <c r="F180">
         <v>16</v>
       </c>
-      <c r="G180" s="2">
+      <c r="G180" s="1">
         <v>45770.976388888892</v>
       </c>
-      <c r="H180" s="1" t="s">
+      <c r="H180" t="s">
         <v>393</v>
       </c>
-      <c r="I180" s="1" t="s">
+      <c r="I180" t="s">
         <v>266</v>
       </c>
-      <c r="J180" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K180" s="1" t="s">
+      <c r="J180" t="s">
+        <v>23</v>
+      </c>
+      <c r="K180" t="s">
         <v>24</v>
       </c>
       <c r="L180">
@@ -12021,29 +12272,28 @@
       <c r="B181">
         <v>100057565135049</v>
       </c>
-      <c r="C181" s="1"/>
-      <c r="D181" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E181" s="1" t="s">
+      <c r="D181" t="s">
+        <v>19</v>
+      </c>
+      <c r="E181" t="s">
         <v>394</v>
       </c>
       <c r="F181">
         <v>0</v>
       </c>
-      <c r="G181" s="2">
+      <c r="G181" s="1">
         <v>45769.938194444447</v>
       </c>
-      <c r="H181" s="1" t="s">
+      <c r="H181" t="s">
         <v>395</v>
       </c>
-      <c r="I181" s="1" t="s">
+      <c r="I181" t="s">
         <v>271</v>
       </c>
-      <c r="J181" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K181" s="1" t="s">
+      <c r="J181" t="s">
+        <v>23</v>
+      </c>
+      <c r="K181" t="s">
         <v>24</v>
       </c>
       <c r="L181">
@@ -12075,29 +12325,28 @@
       <c r="B182">
         <v>100057565135049</v>
       </c>
-      <c r="C182" s="1"/>
-      <c r="D182" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E182" s="1" t="s">
+      <c r="D182" t="s">
+        <v>19</v>
+      </c>
+      <c r="E182" t="s">
         <v>23</v>
       </c>
       <c r="F182">
         <v>0</v>
       </c>
-      <c r="G182" s="2">
+      <c r="G182" s="1">
         <v>45769.159722222219</v>
       </c>
-      <c r="H182" s="1" t="s">
+      <c r="H182" t="s">
         <v>396</v>
       </c>
-      <c r="I182" s="1" t="s">
+      <c r="I182" t="s">
         <v>254</v>
       </c>
-      <c r="J182" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K182" s="1" t="s">
+      <c r="J182" t="s">
+        <v>23</v>
+      </c>
+      <c r="K182" t="s">
         <v>24</v>
       </c>
       <c r="L182">
@@ -12129,29 +12378,28 @@
       <c r="B183">
         <v>100057565135049</v>
       </c>
-      <c r="C183" s="1"/>
-      <c r="D183" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E183" s="1" t="s">
+      <c r="D183" t="s">
+        <v>19</v>
+      </c>
+      <c r="E183" t="s">
         <v>397</v>
       </c>
       <c r="F183">
         <v>0</v>
       </c>
-      <c r="G183" s="2">
+      <c r="G183" s="1">
         <v>45768.980555555558</v>
       </c>
-      <c r="H183" s="1" t="s">
+      <c r="H183" t="s">
         <v>398</v>
       </c>
-      <c r="I183" s="1" t="s">
+      <c r="I183" t="s">
         <v>271</v>
       </c>
-      <c r="J183" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K183" s="1" t="s">
+      <c r="J183" t="s">
+        <v>23</v>
+      </c>
+      <c r="K183" t="s">
         <v>24</v>
       </c>
     </row>
@@ -12162,29 +12410,28 @@
       <c r="B184">
         <v>100057565135049</v>
       </c>
-      <c r="C184" s="1"/>
-      <c r="D184" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E184" s="1" t="s">
+      <c r="D184" t="s">
+        <v>19</v>
+      </c>
+      <c r="E184" t="s">
         <v>399</v>
       </c>
       <c r="F184">
         <v>0</v>
       </c>
-      <c r="G184" s="2">
+      <c r="G184" s="1">
         <v>45756.979861111111</v>
       </c>
-      <c r="H184" s="1" t="s">
+      <c r="H184" t="s">
         <v>400</v>
       </c>
-      <c r="I184" s="1" t="s">
+      <c r="I184" t="s">
         <v>251</v>
       </c>
-      <c r="J184" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K184" s="1" t="s">
+      <c r="J184" t="s">
+        <v>23</v>
+      </c>
+      <c r="K184" t="s">
         <v>24</v>
       </c>
       <c r="L184">
@@ -12216,29 +12463,28 @@
       <c r="B185">
         <v>100057565135049</v>
       </c>
-      <c r="C185" s="1"/>
-      <c r="D185" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E185" s="1" t="s">
+      <c r="D185" t="s">
+        <v>19</v>
+      </c>
+      <c r="E185" t="s">
         <v>401</v>
       </c>
       <c r="F185">
         <v>37</v>
       </c>
-      <c r="G185" s="2">
+      <c r="G185" s="1">
         <v>45750.051388888889</v>
       </c>
-      <c r="H185" s="1" t="s">
+      <c r="H185" t="s">
         <v>402</v>
       </c>
-      <c r="I185" s="1" t="s">
+      <c r="I185" t="s">
         <v>266</v>
       </c>
-      <c r="J185" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K185" s="1" t="s">
+      <c r="J185" t="s">
+        <v>23</v>
+      </c>
+      <c r="K185" t="s">
         <v>24</v>
       </c>
       <c r="L185">
@@ -12270,29 +12516,28 @@
       <c r="B186">
         <v>100057565135049</v>
       </c>
-      <c r="C186" s="1"/>
-      <c r="D186" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E186" s="1" t="s">
+      <c r="D186" t="s">
+        <v>19</v>
+      </c>
+      <c r="E186" t="s">
         <v>403</v>
       </c>
       <c r="F186">
         <v>0</v>
       </c>
-      <c r="G186" s="2">
+      <c r="G186" s="1">
         <v>45747.084027777775</v>
       </c>
-      <c r="H186" s="1" t="s">
+      <c r="H186" t="s">
         <v>404</v>
       </c>
-      <c r="I186" s="1" t="s">
+      <c r="I186" t="s">
         <v>251</v>
       </c>
-      <c r="J186" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K186" s="1" t="s">
+      <c r="J186" t="s">
+        <v>23</v>
+      </c>
+      <c r="K186" t="s">
         <v>24</v>
       </c>
       <c r="L186">
@@ -12324,29 +12569,28 @@
       <c r="B187">
         <v>100057565135049</v>
       </c>
-      <c r="C187" s="1"/>
-      <c r="D187" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E187" s="1" t="s">
+      <c r="D187" t="s">
+        <v>19</v>
+      </c>
+      <c r="E187" t="s">
         <v>405</v>
       </c>
       <c r="F187">
         <v>0</v>
       </c>
-      <c r="G187" s="2">
+      <c r="G187" s="1">
         <v>45743.038194444445</v>
       </c>
-      <c r="H187" s="1" t="s">
+      <c r="H187" t="s">
         <v>406</v>
       </c>
-      <c r="I187" s="1" t="s">
+      <c r="I187" t="s">
         <v>251</v>
       </c>
-      <c r="J187" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K187" s="1" t="s">
+      <c r="J187" t="s">
+        <v>23</v>
+      </c>
+      <c r="K187" t="s">
         <v>24</v>
       </c>
       <c r="L187">
@@ -12378,29 +12622,28 @@
       <c r="B188">
         <v>100057565135049</v>
       </c>
-      <c r="C188" s="1"/>
-      <c r="D188" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E188" s="1" t="s">
+      <c r="D188" t="s">
+        <v>19</v>
+      </c>
+      <c r="E188" t="s">
         <v>407</v>
       </c>
       <c r="F188">
         <v>0</v>
       </c>
-      <c r="G188" s="2">
+      <c r="G188" s="1">
         <v>45729.07916666667</v>
       </c>
-      <c r="H188" s="1" t="s">
+      <c r="H188" t="s">
         <v>408</v>
       </c>
-      <c r="I188" s="1" t="s">
+      <c r="I188" t="s">
         <v>251</v>
       </c>
-      <c r="J188" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K188" s="1" t="s">
+      <c r="J188" t="s">
+        <v>23</v>
+      </c>
+      <c r="K188" t="s">
         <v>24</v>
       </c>
       <c r="L188">
@@ -12432,29 +12675,28 @@
       <c r="B189">
         <v>100057565135049</v>
       </c>
-      <c r="C189" s="1"/>
-      <c r="D189" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E189" s="1" t="s">
+      <c r="D189" t="s">
+        <v>19</v>
+      </c>
+      <c r="E189" t="s">
         <v>409</v>
       </c>
       <c r="F189">
         <v>0</v>
       </c>
-      <c r="G189" s="2">
+      <c r="G189" s="1">
         <v>45726.081944444442</v>
       </c>
-      <c r="H189" s="1" t="s">
+      <c r="H189" t="s">
         <v>410</v>
       </c>
-      <c r="I189" s="1" t="s">
+      <c r="I189" t="s">
         <v>251</v>
       </c>
-      <c r="J189" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K189" s="1" t="s">
+      <c r="J189" t="s">
+        <v>23</v>
+      </c>
+      <c r="K189" t="s">
         <v>24</v>
       </c>
       <c r="L189">
@@ -12486,29 +12728,28 @@
       <c r="B190">
         <v>100057565135049</v>
       </c>
-      <c r="C190" s="1"/>
-      <c r="D190" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E190" s="1" t="s">
+      <c r="D190" t="s">
+        <v>19</v>
+      </c>
+      <c r="E190" t="s">
         <v>411</v>
       </c>
       <c r="F190">
         <v>0</v>
       </c>
-      <c r="G190" s="2">
+      <c r="G190" s="1">
         <v>45721.990277777775</v>
       </c>
-      <c r="H190" s="1" t="s">
+      <c r="H190" t="s">
         <v>412</v>
       </c>
-      <c r="I190" s="1" t="s">
+      <c r="I190" t="s">
         <v>254</v>
       </c>
-      <c r="J190" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K190" s="1" t="s">
+      <c r="J190" t="s">
+        <v>23</v>
+      </c>
+      <c r="K190" t="s">
         <v>24</v>
       </c>
       <c r="L190">
@@ -12540,29 +12781,28 @@
       <c r="B191">
         <v>100057565135049</v>
       </c>
-      <c r="C191" s="1"/>
-      <c r="D191" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E191" s="1" t="s">
+      <c r="D191" t="s">
+        <v>19</v>
+      </c>
+      <c r="E191" t="s">
         <v>413</v>
       </c>
       <c r="F191">
         <v>0</v>
       </c>
-      <c r="G191" s="2">
+      <c r="G191" s="1">
         <v>45702.029861111114</v>
       </c>
-      <c r="H191" s="1" t="s">
+      <c r="H191" t="s">
         <v>414</v>
       </c>
-      <c r="I191" s="1" t="s">
+      <c r="I191" t="s">
         <v>251</v>
       </c>
-      <c r="J191" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K191" s="1" t="s">
+      <c r="J191" t="s">
+        <v>23</v>
+      </c>
+      <c r="K191" t="s">
         <v>24</v>
       </c>
       <c r="L191">
@@ -12594,29 +12834,28 @@
       <c r="B192">
         <v>100057565135049</v>
       </c>
-      <c r="C192" s="1"/>
-      <c r="D192" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E192" s="1" t="s">
+      <c r="D192" t="s">
+        <v>19</v>
+      </c>
+      <c r="E192" t="s">
         <v>415</v>
       </c>
       <c r="F192">
         <v>0</v>
       </c>
-      <c r="G192" s="2">
+      <c r="G192" s="1">
         <v>45693.968055555553</v>
       </c>
-      <c r="H192" s="1" t="s">
+      <c r="H192" t="s">
         <v>416</v>
       </c>
-      <c r="I192" s="1" t="s">
+      <c r="I192" t="s">
         <v>251</v>
       </c>
-      <c r="J192" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K192" s="1" t="s">
+      <c r="J192" t="s">
+        <v>23</v>
+      </c>
+      <c r="K192" t="s">
         <v>24</v>
       </c>
       <c r="L192">
@@ -12648,29 +12887,28 @@
       <c r="B193">
         <v>100057565135049</v>
       </c>
-      <c r="C193" s="1"/>
-      <c r="D193" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E193" s="1" t="s">
+      <c r="D193" t="s">
+        <v>19</v>
+      </c>
+      <c r="E193" t="s">
         <v>417</v>
       </c>
       <c r="F193">
         <v>0</v>
       </c>
-      <c r="G193" s="2">
+      <c r="G193" s="1">
         <v>45686.03125</v>
       </c>
-      <c r="H193" s="1" t="s">
+      <c r="H193" t="s">
         <v>418</v>
       </c>
-      <c r="I193" s="1" t="s">
+      <c r="I193" t="s">
         <v>251</v>
       </c>
-      <c r="J193" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K193" s="1" t="s">
+      <c r="J193" t="s">
+        <v>23</v>
+      </c>
+      <c r="K193" t="s">
         <v>24</v>
       </c>
       <c r="L193">
@@ -12702,29 +12940,28 @@
       <c r="B194">
         <v>100057565135049</v>
       </c>
-      <c r="C194" s="1"/>
-      <c r="D194" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E194" s="1" t="s">
+      <c r="D194" t="s">
+        <v>19</v>
+      </c>
+      <c r="E194" t="s">
         <v>419</v>
       </c>
       <c r="F194">
         <v>0</v>
       </c>
-      <c r="G194" s="2">
+      <c r="G194" s="1">
         <v>45670.991666666669</v>
       </c>
-      <c r="H194" s="1" t="s">
+      <c r="H194" t="s">
         <v>420</v>
       </c>
-      <c r="I194" s="1" t="s">
+      <c r="I194" t="s">
         <v>251</v>
       </c>
-      <c r="J194" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K194" s="1" t="s">
+      <c r="J194" t="s">
+        <v>23</v>
+      </c>
+      <c r="K194" t="s">
         <v>24</v>
       </c>
       <c r="L194">
@@ -12747,6 +12984,602 @@
       </c>
       <c r="T194">
         <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD75E68A-5DA0-404B-AC3D-27ACBA9DC058}">
+  <dimension ref="A1:D25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C1" t="s">
+        <v>423</v>
+      </c>
+      <c r="D1" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>425</v>
+      </c>
+      <c r="B2" t="s">
+        <v>426</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="D2" s="3">
+        <v>9.0000000000000011E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>425</v>
+      </c>
+      <c r="B3" t="s">
+        <v>426</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="D3" s="5">
+        <v>5.2000000000000005E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>425</v>
+      </c>
+      <c r="B4" t="s">
+        <v>426</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>425</v>
+      </c>
+      <c r="B5" t="s">
+        <v>426</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="D5" s="5">
+        <v>0.11699999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>425</v>
+      </c>
+      <c r="B6" t="s">
+        <v>426</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="D6" s="3">
+        <v>8.900000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>425</v>
+      </c>
+      <c r="B7" t="s">
+        <v>426</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="D7" s="5">
+        <v>4.8000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>425</v>
+      </c>
+      <c r="B8" t="s">
+        <v>433</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="D8" s="3">
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>425</v>
+      </c>
+      <c r="B9" t="s">
+        <v>433</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="D9" s="5">
+        <v>6.5000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>425</v>
+      </c>
+      <c r="B10" t="s">
+        <v>433</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0.13400000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>425</v>
+      </c>
+      <c r="B11" t="s">
+        <v>433</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0.222</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>425</v>
+      </c>
+      <c r="B12" t="s">
+        <v>433</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>425</v>
+      </c>
+      <c r="B13" t="s">
+        <v>433</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>434</v>
+      </c>
+      <c r="B14" t="s">
+        <v>426</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="D14" s="6">
+        <v>1.6E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>434</v>
+      </c>
+      <c r="B15" t="s">
+        <v>426</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="D15" s="7">
+        <v>7.6999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>434</v>
+      </c>
+      <c r="B16" t="s">
+        <v>426</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="D16" s="6">
+        <v>9.6000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>434</v>
+      </c>
+      <c r="B17" t="s">
+        <v>426</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="D17" s="7">
+        <v>0.128</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>434</v>
+      </c>
+      <c r="B18" t="s">
+        <v>426</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="D18" s="6">
+        <v>6.9000000000000006E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>434</v>
+      </c>
+      <c r="B19" t="s">
+        <v>426</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="D19" s="7">
+        <v>3.3000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>434</v>
+      </c>
+      <c r="B20" t="s">
+        <v>433</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="D20" s="8">
+        <v>3.6000000000000004E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>434</v>
+      </c>
+      <c r="B21" t="s">
+        <v>433</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="D21" s="9">
+        <v>7.5999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>434</v>
+      </c>
+      <c r="B22" t="s">
+        <v>433</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="D22" s="8">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>434</v>
+      </c>
+      <c r="B23" t="s">
+        <v>433</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="D23" s="9">
+        <v>0.17600000000000002</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>434</v>
+      </c>
+      <c r="B24" t="s">
+        <v>433</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="D24" s="8">
+        <v>9.3000000000000013E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>434</v>
+      </c>
+      <c r="B25" t="s">
+        <v>433</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="D25" s="9">
+        <v>0.03</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{849B0C14-3CA1-47D9-A45B-A7B4FE179856}">
+  <dimension ref="A1:C19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C1" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>425</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0.29600000000000004</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>425</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>437</v>
+      </c>
+      <c r="C3" s="11">
+        <v>5.0999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>425</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="C4" s="11">
+        <v>4.9000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>425</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>439</v>
+      </c>
+      <c r="C5" s="11">
+        <v>4.8000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>425</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>440</v>
+      </c>
+      <c r="C6" s="11">
+        <v>3.9E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>425</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>441</v>
+      </c>
+      <c r="C7" s="11">
+        <v>3.4000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>425</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>442</v>
+      </c>
+      <c r="C8" s="9">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>425</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>443</v>
+      </c>
+      <c r="C9" s="11">
+        <v>1.8000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>425</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>444</v>
+      </c>
+      <c r="C10" s="13">
+        <v>1.6E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>434</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="C11" s="9">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>434</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="C12" s="10">
+        <v>6.5000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>434</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="C13" s="9">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>434</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C14" s="10">
+        <v>4.4000000000000004E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>434</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="C15" s="11">
+        <v>3.3000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>434</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="C16" s="10">
+        <v>2.8999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>434</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="C17" s="11">
+        <v>2.6000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>434</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="C18" s="10">
+        <v>2.2000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>434</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="C19" s="11">
+        <v>1.7000000000000001E-2</v>
       </c>
     </row>
   </sheetData>

--- a/rådata.xlsx
+++ b/rådata.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="229" documentId="11_AD4D1D646341095ACB7000BA6D52DEAE693EDF20" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D4C7E51-D958-45DE-A92E-86FB8FB99FB6}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="rådata" sheetId="2" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14003" uniqueCount="2239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13918" uniqueCount="2239">
   <si>
     <t>Post ID</t>
   </si>
